--- a/設計書/設計書.xlsx
+++ b/設計書/設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\computer-visualizer\設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00147E1A-B2AB-4973-943B-9942BC16433A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE3F695-8C92-4689-B641-56E2FD0EE948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,13 +25,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>スタック</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>○○フレーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディスク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>← num</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -69,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -81,21 +93,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -198,51 +195,40 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -295,10 +281,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg1"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -326,6 +309,43 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ただのテキストエディタ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>main(){</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>int</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t> num = 5;</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>}</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -622,6 +642,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>319547</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>32774</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>153353</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>151132</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88B8B2A4-4BC1-F806-81A7-589C21037B40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10397612" y="1179871"/>
+          <a:ext cx="7224386" cy="3330229"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -892,668 +956,281 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="3" spans="3:15">
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="9"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="8"/>
     </row>
     <row r="4" spans="3:15">
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="12"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="11"/>
     </row>
     <row r="5" spans="3:15">
       <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="3"/>
+      <c r="I5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" spans="3:15">
       <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3"/>
+      <c r="I6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" spans="3:15">
       <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="3"/>
+      <c r="I7" s="2"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="3:15">
       <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="3:15">
       <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="3"/>
+      <c r="I9" s="2"/>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" spans="3:15">
-      <c r="C10" s="15"/>
+      <c r="C10" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="D10" s="14"/>
-      <c r="E10" s="2"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="3"/>
+      <c r="H10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="O10" s="2"/>
     </row>
     <row r="11" spans="3:15">
       <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="3"/>
+      <c r="I11" s="2"/>
+      <c r="O11" s="2"/>
     </row>
     <row r="12" spans="3:15">
       <c r="C12" s="1"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="3"/>
+      <c r="I12" s="2"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="3:15">
       <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="3"/>
+      <c r="I13" s="2"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" spans="3:15">
       <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="3"/>
+      <c r="I14" s="2"/>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" spans="3:15">
       <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="3"/>
+      <c r="I15" s="2"/>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" spans="3:15">
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D16" s="14"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="3"/>
+      <c r="I16" s="2"/>
+      <c r="O16" s="2"/>
     </row>
     <row r="17" spans="3:15">
       <c r="C17" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="3"/>
+      <c r="D17" s="15"/>
+      <c r="I17" s="2"/>
+      <c r="O17" s="2"/>
     </row>
     <row r="18" spans="3:15">
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="3"/>
+      <c r="C18" s="12">
+        <v>5</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="O18" s="2"/>
     </row>
     <row r="19" spans="3:15">
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="3"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="16"/>
+      <c r="I19" s="2"/>
+      <c r="O19" s="2"/>
     </row>
     <row r="20" spans="3:15">
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="3"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="16"/>
+      <c r="I20" s="2"/>
+      <c r="O20" s="2"/>
     </row>
     <row r="21" spans="3:15">
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="3"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="16"/>
+      <c r="I21" s="2"/>
+      <c r="O21" s="2"/>
     </row>
     <row r="22" spans="3:15">
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="3"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="16"/>
+      <c r="I22" s="2"/>
+      <c r="O22" s="2"/>
     </row>
     <row r="23" spans="3:15">
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="3"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="16"/>
+      <c r="I23" s="2"/>
+      <c r="O23" s="2"/>
     </row>
     <row r="24" spans="3:15">
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="3"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="16"/>
+      <c r="I24" s="2"/>
+      <c r="O24" s="2"/>
     </row>
     <row r="25" spans="3:15">
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="3"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="16"/>
+      <c r="I25" s="2"/>
+      <c r="O25" s="2"/>
     </row>
     <row r="26" spans="3:15">
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="16"/>
+      <c r="I26" s="2"/>
+      <c r="O26" s="2"/>
     </row>
     <row r="27" spans="3:15">
       <c r="C27" s="1"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="3"/>
+      <c r="I27" s="2"/>
+      <c r="O27" s="2"/>
     </row>
     <row r="28" spans="3:15">
       <c r="C28" s="1"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="3"/>
+      <c r="I28" s="2"/>
+      <c r="O28" s="2"/>
     </row>
     <row r="29" spans="3:15">
       <c r="C29" s="1"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="3"/>
+      <c r="I29" s="2"/>
+      <c r="O29" s="2"/>
     </row>
     <row r="30" spans="3:15">
       <c r="C30" s="1"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="3"/>
+      <c r="I30" s="2"/>
+      <c r="O30" s="2"/>
     </row>
     <row r="31" spans="3:15">
       <c r="C31" s="1"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="3"/>
+      <c r="I31" s="2"/>
+      <c r="O31" s="2"/>
     </row>
     <row r="32" spans="3:15">
       <c r="C32" s="1"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="3"/>
+      <c r="I32" s="2"/>
+      <c r="O32" s="2"/>
     </row>
     <row r="33" spans="3:15">
       <c r="C33" s="1"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="3"/>
+      <c r="I33" s="2"/>
+      <c r="O33" s="2"/>
     </row>
     <row r="34" spans="3:15">
       <c r="C34" s="1"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="3"/>
+      <c r="I34" s="2"/>
+      <c r="O34" s="2"/>
     </row>
     <row r="35" spans="3:15">
       <c r="C35" s="1"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="3"/>
+      <c r="I35" s="2"/>
+      <c r="O35" s="2"/>
     </row>
     <row r="36" spans="3:15">
       <c r="C36" s="1"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="3"/>
+      <c r="I36" s="2"/>
+      <c r="O36" s="2"/>
     </row>
     <row r="37" spans="3:15">
       <c r="C37" s="1"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="3"/>
+      <c r="I37" s="2"/>
+      <c r="O37" s="2"/>
     </row>
     <row r="38" spans="3:15">
       <c r="C38" s="1"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="3"/>
+      <c r="I38" s="2"/>
+      <c r="O38" s="2"/>
     </row>
     <row r="39" spans="3:15">
       <c r="C39" s="1"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="3"/>
+      <c r="I39" s="2"/>
+      <c r="O39" s="2"/>
     </row>
     <row r="40" spans="3:15">
       <c r="C40" s="1"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="3"/>
+      <c r="I40" s="2"/>
+      <c r="O40" s="2"/>
     </row>
     <row r="41" spans="3:15">
       <c r="C41" s="1"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="3"/>
+      <c r="I41" s="2"/>
+      <c r="O41" s="2"/>
     </row>
     <row r="42" spans="3:15">
       <c r="C42" s="1"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="3"/>
+      <c r="I42" s="2"/>
+      <c r="O42" s="2"/>
     </row>
     <row r="43" spans="3:15">
       <c r="C43" s="1"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="3"/>
+      <c r="I43" s="2"/>
+      <c r="O43" s="2"/>
     </row>
     <row r="44" spans="3:15">
       <c r="C44" s="1"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="3"/>
+      <c r="I44" s="2"/>
+      <c r="O44" s="2"/>
     </row>
     <row r="45" spans="3:15">
       <c r="C45" s="1"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="3"/>
+      <c r="I45" s="2"/>
+      <c r="O45" s="2"/>
     </row>
     <row r="46" spans="3:15">
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="6"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1564,6 +1241,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/設計書/設計書.xlsx
+++ b/設計書/設計書.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\computer-visualizer\設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE3F695-8C92-4689-B641-56E2FD0EE948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0738CA6-6CA3-4C25-B771-64FA3A63F2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="概要" sheetId="1" r:id="rId1"/>
+    <sheet name="具体的" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>スタック</t>
     <phoneticPr fontId="1"/>
@@ -44,6 +45,58 @@
   </si>
   <si>
     <t>← num</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーサー（Parser）とは、コンピュータの世界では文章やコードなどの構造化されていないデータを解析し、プログラムが理解できるデータ構造に変換する仕組み（構文解析器）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AST（抽象構文木）とは、コードを「コンピュータが扱いやすい木構造」にしたもの</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：JS</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・解析対象言語…C#</t>
+    <rPh sb="1" eb="5">
+      <t>カイセキタイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・C#AST…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・C#パーサー…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・エディタ…Monaco</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Roslynは、そもそもC#のコンパイラ基盤そのものなので、C#コードを解析してSyntax Tree（構文木）を作る機能を持っている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>構文としての条件をそのコードが満たしているか(例えば「inti t = #」みたいな構文としての条件を満たしていないコードがかかれたら何も起こらないという仕様にしたい)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→これもRoslynが判定して(シンタックスerrorだしてくれる)→そのままreturn</t>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -215,20 +268,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -686,7 +739,1450 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>58209</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>146345</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>375285</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>227953</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="21" name="インク 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E8A0C3-6572-E4CD-6CC3-1DD914F83377}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="730080" y="3128797"/>
+            <a:ext cx="3004560" cy="2834640"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="インク 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E8A0C3-6572-E4CD-6CC3-1DD914F83377}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="694084" y="3093157"/>
+              <a:ext cx="3076191" cy="2906280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>582285</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>137891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>8610</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>34074</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="37" name="インク 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{100C73D3-7FA3-6EE7-1189-2E4CEB3AE9E2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3941640" y="5185117"/>
+            <a:ext cx="2785680" cy="1043280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="37" name="インク 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{100C73D3-7FA3-6EE7-1189-2E4CEB3AE9E2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3906000" y="5149117"/>
+              <a:ext cx="2857320" cy="1114920"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>432219</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>208228</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>24615</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>208650</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="57" name="インク 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A0C6DEA-2A19-6F1A-DABE-4D70D6ADEE08}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7822800" y="4108357"/>
+            <a:ext cx="2279880" cy="688680"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="57" name="インク 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A0C6DEA-2A19-6F1A-DABE-4D70D6ADEE08}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7786800" y="4072376"/>
+              <a:ext cx="2351520" cy="760283"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>245796</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>122102</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>77619</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>166530</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="58" name="インク 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC02053-C5F2-4F6A-B329-F00BD948FE61}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2933280" y="1728037"/>
+            <a:ext cx="4534920" cy="3026880"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="58" name="インク 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC02053-C5F2-4F6A-B329-F00BD948FE61}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2897640" y="1692397"/>
+              <a:ext cx="4606560" cy="3098520"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>180690</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>111971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>580068</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>87454</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="73" name="インク 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFE15520-D428-F32D-AF0D-ED3E340DA8A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6899400" y="5159197"/>
+            <a:ext cx="1743120" cy="893160"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="73" name="インク 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFE15520-D428-F32D-AF0D-ED3E340DA8A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6863393" y="5123543"/>
+              <a:ext cx="1814775" cy="964829"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>544095</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>181985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>210154</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>196745</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="74" name="インク 73">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A14C5D46-CD11-637F-2167-20FE3C53C5EA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10622160" y="3164437"/>
+            <a:ext cx="1009800" cy="14760"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="74" name="インク 73">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A14C5D46-CD11-637F-2167-20FE3C53C5EA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10586520" y="3128437"/>
+              <a:ext cx="1081440" cy="86400"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>550215</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>237154</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>120587</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="75" name="インク 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70857AFB-0CD4-C3EC-DF6B-B9535BF82F96}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10628280" y="3507517"/>
+            <a:ext cx="1030680" cy="54360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="75" name="インク 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70857AFB-0CD4-C3EC-DF6B-B9535BF82F96}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10592280" y="3471877"/>
+              <a:ext cx="1102320" cy="126000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>517095</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>115708</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>150754</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>139108</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="76" name="インク 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDB16D33-EAF4-3A9B-1FA3-1CB9E14010E8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10595160" y="4015837"/>
+            <a:ext cx="977400" cy="23400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="76" name="インク 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDB16D33-EAF4-3A9B-1FA3-1CB9E14010E8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10559520" y="3979837"/>
+              <a:ext cx="1049040" cy="95040"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>432135</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>39549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>246514</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>119829</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="77" name="インク 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51A8E941-4835-817C-EBBB-1D37F7FBD7D9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10510200" y="4398517"/>
+            <a:ext cx="1158120" cy="80280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="77" name="インク 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51A8E941-4835-817C-EBBB-1D37F7FBD7D9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10474560" y="4362517"/>
+              <a:ext cx="1229760" cy="151920"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>387357</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>168380</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>603634</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>153645</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="86" name="インク 85">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EFD229D-2691-65B0-756B-8B7D379EDA04}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9121680" y="1315477"/>
+            <a:ext cx="2903760" cy="1591200"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="86" name="インク 85">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EFD229D-2691-65B0-756B-8B7D379EDA04}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9086040" y="1279477"/>
+              <a:ext cx="2975400" cy="1662840"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>312658</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>91708</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1E50048-DEDA-D455-2950-8090B27B2EFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="251460" y="198120"/>
+          <a:ext cx="2743438" cy="3093988"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>381252</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>221142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80592393-6936-FA6B-FB20-2EFE956898C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2164080" y="1325880"/>
+          <a:ext cx="2911092" cy="1867062"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>560012</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>328036</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>15763</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A36EFC1-353B-8665-4C0F-DAB0D12B22FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5253932" y="1165860"/>
+          <a:ext cx="3120824" cy="4336303"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>640503</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>106938</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2F7262-9B89-25C6-B747-47A476E10754}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="457200" y="6050280"/>
+          <a:ext cx="4877223" cy="2972058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E083EC-60A9-1D88-D8D2-3F2FCD0AC144}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="9349740"/>
+          <a:ext cx="4206240" cy="4023360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Angualr</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>↓</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>エディタの入力値取得</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>一文</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>して</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>JSON</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>化</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>↓</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>API</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Roslyn</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>でパース</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>AST</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Syntax Tree</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>）作成</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>「フロントが描画するために必要な情報」をまとめた</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>SimulationState</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>オブジェクト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>画面用の状態データ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>JSON</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Angular</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>描画</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:09.334"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4419 7735 11979 0 0,'-116'45'4259'0'0,"-91"28"-3504"0"0,182-67-653 0 0,-1-1-1 0 0,1-1 1 0 0,-1-1-1 0 0,0-1 1 0 0,0-1-1 0 0,-42-5 1 0 0,-461-49 1450 0 0,-157-29-389 0 0,515 53-618 0 0,-296-91 1 0 0,375 88-446 0 0,2-3 1 0 0,1-5-1 0 0,2-3 1 0 0,-138-93 0 0 0,142 71-72 0 0,-137-139 1 0 0,131 117-5 0 0,17 18-33 0 0,3-4 0 0 0,3-2 0 0 0,3-3 0 0 0,-53-87 0 0 0,-4-40-54 0 0,9-6 0 0 0,-94-251 0 0 0,157 332 35 0 0,6-1 1 0 0,5-3-1 0 0,7-1 0 0 0,5-1 0 0 0,-10-210 0 0 0,28 63-57 0 0,13-1-1 0 0,43-286 1 0 0,-29 453 30 0 0,5 0 0 0 0,77-218 0 0 0,134-204-181 0 0,-172 417 144 0 0,6 4 0 0 0,4 3 0 0 0,129-152 0 0 0,315-272-313 0 0,-381 418 402 0 0,247-170 0 0 0,190-47-2 0 0,-434 270-33 0 0,3 6-1 0 0,253-73 0 0 0,-187 82-35 0 0,298-37 1 0 0,-361 74-5 0 0,1 6 1 0 0,0 7 0 0 0,1 6 0 0 0,-1 6-1 0 0,194 38 1 0 0,-237-26 118 0 0,-1 6 0 0 0,-2 3 0 0 0,-1 5 1 0 0,-1 5-1 0 0,-2 3 0 0 0,-3 5 0 0 0,-1 4 0 0 0,99 74 0 0 0,188 186 222 0 0,-308-244-189 0 0,-4 4 1 0 0,115 155 0 0 0,129 274 128 0 0,-255-392-156 0 0,-5 2 0 0 0,66 211 0 0 0,-78-171 10 0 0,-8 2 0 0 0,-5 1 1 0 0,-8 1-1 0 0,-6 1 1 0 0,-8 1-1 0 0,-6-1 0 0 0,-40 297 1 0 0,17-323 18 0 0,-5-1 0 0 0,-87 234 0 0 0,50-202 94 0 0,-149 259 0 0 0,-7-60 58 0 0,146-251-115 0 0,-104 117-1 0 0,-2-27 169 0 0,-360 304 0 0 0,177-221-73 0 0,259-209-127 0 0,-180 94 1 0 0,122-88-483 0 0,-336 114-1 0 0,386-159-951 0 0,-2-4-1 0 0,-1-5 1 0 0,-220 16-1 0 0,180-36-5878 0 0,-168-16 0 0 0,247 3 4692 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1568.07">6450 5639 7618 0 0,'-3'-10'3906'0'0,"4"9"-3834"0"0,-1 1-71 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,5 44 283 0 0,-2 1 0 0 0,-3-1 1 0 0,-5 57-1 0 0,2-57-182 0 0,-28 344 202 0 0,-96 459 1 0 0,117-805-509 0 0,3-12-694 0 0,1 1 0 0 0,1 0 1 0 0,0 57-1 0 0,8-71-1514 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1819.2">6515 5556 11779 0 0,'0'-1'62'0'0,"-1"0"0"0"0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,33-14-445 0 0,-25 11 598 0 0,24-7-115 0 0,1 1 0 0 0,-1 2 0 0 0,1 1 0 0 0,1 2 0 0 0,-1 2 0 0 0,56 0-1 0 0,216 29 24 0 0,-295-25-110 0 0,374 71-4666 0 0,-380-71 4385 0 0,42 13-4311 0 0,96 39-415 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2119.47">6647 5492 14227 0 0,'0'0'17'0'0,"0"0"-1"0"0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,15-4-61 0 0,24 1-257 0 0,-17 3 321 0 0,-1 1 0 0 0,0 0 0 0 0,1 2 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 2 0 0 0,-1 0 0 0 0,20 10 0 0 0,-14-3 7 0 0,0 1 1 0 0,-2 1-1 0 0,0 1 0 0 0,-1 1 0 0 0,39 38 0 0 0,-23-13 13 0 0,-1 2 0 0 0,35 53 0 0 0,53 102 32 0 0,-114-180-66 0 0,141 235 78 0 0,98 162-2183 0 0,-78-144-2921 0 0,-35-76 206 0 0,-111-161 3685 0 0,-21-27 818 0 0,-1-2 90 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,13 11 1 0 0,138 118-797 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink10.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:53.503"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3472 602 8442 0 0,'6'43'2829'0'0,"3"20"-3271"0"0,-12 122 674 0 0,-31 205-1 0 0,15-209-189 0 0,-80 620 41 0 0,5-42 44 0 0,74-448-275 0 0,20-248 104 0 0,2 0 0 0 0,22 118 0 0 0,-22-170 43 0 0,1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,10 17 0 0 0,-12-23 7 0 0,0-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,9 4 0 0 0,19 0 150 0 0,0 0 0 0 0,0-3 0 0 0,0 0-1 0 0,0-2 1 0 0,45-5 0 0 0,-42 2-77 0 0,731 4 587 0 0,0 33-523 0 0,-214-8-269 0 0,1366 6 45 0 0,-1700-41-865 0 0,-79-7-4227 0 0,-126 12 1822 0 0,21-8-172 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="490.51">3606 391 11707 0 0,'-7'-13'-40'0'0,"5"9"6"0"0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1-5 0 0 0,2 9-24 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,3 0 0 0 0,3-2-94 0 0,342-90-89 0 0,117-27 499 0 0,-326 90-168 0 0,195-15 0 0 0,-41 31-135 0 0,455 40 0 0 0,-246 41-71 0 0,-7 30 306 0 0,-432-84-110 0 0,-17-4 244 0 0,-1 2 1 0 0,91 35-1 0 0,-117-37-209 0 0,0 1 0 0 0,0 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 2-1 0 0,-1 0 1 0 0,0 1 0 0 0,18 22 0 0 0,-11-7-59 0 0,-2 1 0 0 0,-2 1 0 0 0,-1 2 0 0 0,-1 0 0 0 0,-2 0 0 0 0,-1 2 0 0 0,-2 0 0 0 0,-2 1 0 0 0,-1 0 0 0 0,9 67 0 0 0,-7 0 163 0 0,-6 0 1 0 0,-9 194-1 0 0,-51 250 356 0 0,-31 0-435 0 0,25-181-260 0 0,-7 99-290 0 0,-73 447-730 0 0,132-877 970 0 0,-12 59-2327 0 0,16-85 962 0 0,0 0 0 0 0,-1 0 0 0 0,-7 12 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1443.25">82 1535 8514 0 0,'79'-71'4148'0'0,"-56"53"-4142"0"0,0 1 0 0 0,0 1 0 0 0,2 1 0 0 0,0 1 0 0 0,0 1 0 0 0,43-14 0 0 0,111-24-170 0 0,-156 46-13 0 0,1 1 0 0 0,0 1 0 0 0,0 1-1 0 0,0 2 1 0 0,42 3 0 0 0,-61-3 124 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,4 7-1 0 0,-4-4 41 0 0,0 1 0 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 10 0 0 0,-3 5 38 0 0,0 1 1 0 0,-2-1-1 0 0,-1 0 0 0 0,0-1 0 0 0,-16 32 0 0 0,4-16 8 0 0,-1-1-1 0 0,-32 45 0 0 0,30-54 39 0 0,0-1 0 0 0,-2-1 1 0 0,-1-1-1 0 0,-44 35 0 0 0,23-27 28 0 0,-1-2 0 0 0,-58 30-1 0 0,65-40 63 0 0,-1-2-1 0 0,-46 15 1 0 0,87-34-260 0 0,1 5-8 0 0,1 0 0 0 0,-1 0 0 0 0,2 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,2-1 0 0 0,-1 1 0 0 0,5 4-1 0 0,9 19 140 0 0,-10-12 20 0 0,0 1-1 0 0,-1 0 1 0 0,-1-1 0 0 0,0 2-1 0 0,-1-1 1 0 0,-1 0 0 0 0,-1 1-1 0 0,-1 0 1 0 0,-2 30 0 0 0,-4-2 41 0 0,-2-1 1 0 0,-22 77-1 0 0,-21 89 150 0 0,-41 132-68 0 0,26-134-3531 0 0,59-192-596 0 0,0 28-388 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1632.32">804 2021 17588 0 0,'0'-16'488'0'0,"3"4"80"0"0,0 3-968 0 0,12 8-72 0 0,7-5 32 0 0,17 1-8 0 0,14 1 176 0 0,11-2-569 0 0,2-2-415 0 0,1 2-112 0 0,-3 1-1425 0 0,44 3-7553 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1805.68">1430 2668 16347 0 0,'21'-16'2537'0'0,"9"-5"-2489"0"0,11-3 32 0 0,19-2-176 0 0,11 0-256 0 0,14 4-336 0 0,1 0-104 0 0,-2-1-81 0 0,-4 0-335 0 0,-4-4-1384 0 0,-6 2-1305 0 0,3 1-272 0 0,1 0 4217 0 0,-7 3-2249 0 0,-5 0 17 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1979.88">2219 1889 16283 0 0,'0'0'1761'0'0,"5"7"-1913"0"0,10 13-120 0 0,12 15-320 0 0,9 15 704 0 0,8 16 24 0 0,3 4 0 0 0,0-1-16 0 0,1-2-120 0 0,-1-9-872 0 0,-1-3-513 0 0,-2-3-159 0 0,-3-2-1561 0 0,38 32-7513 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2170.56">2831 1547 16692 0 0,'-5'2'23'0'0,"0"0"-1"0"0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-5 7 0 0 0,-3 7-142 0 0,0 2 0 0 0,-9 21 0 0 0,9-18 171 0 0,-79 170-91 0 0,20-37-655 0 0,-127 205 0 0 0,146-284-254 0 0,-109 183-7764 0 0,73-106 5621 0 0,45-90 569 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:15.059"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">179 2126 15707 0 0,'-35'-2'3609'0'0,"6"2"-2265"0"0,11 0-727 0 0,13-1-177 0 0,27-5-1825 0 0,12-4 825 0 0,17-5 0 0 0,10-6 632 0 0,10-4-256 0 0,3 1-416 0 0,8-2 32 0 0,7 3-1097 0 0,7 0-1391 0 0,-3 3 1920 0 0,-3 3-4906 0 0,-16 2 17 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="538.35">2071 1877 13547 0 0,'-89'3'5108'0'0,"175"-17"-5492"0"0,95-28 0 0 0,-25 5-1684 0 0,184-15-7195 0 0,-311 48 7677 0 0,45-6-3376 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="918.79">3794 728 9898 0 0,'-12'-6'2833'0'0,"14"1"-2257"0"0,9 5-1184 0 0,7-3 496 0 0,9-1 24 0 0,18-2 136 0 0,7-2-8 0 0,13-3-40 0 0,5-3 32 0 0,-3 4-40 0 0,-1-1-232 0 0,-7 4-2241 0 0,-4 2 1681 0 0,-7-2-3745 0 0,-8 0 8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1124.18">4371 548 2809 0 0,'-8'1'1442'0'0,"1"0"1"0"0,-1 1 0 0 0,1-1 0 0 0,-1 2 0 0 0,-12 5 0 0 0,14-5-1131 0 0,0 1 1 0 0,1-1 0 0 0,0 1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,1 0-1 0 0,-7 11 1 0 0,-11 24 197 0 0,1 1 0 0 0,-22 68 0 0 0,-16 92 126 0 0,48-163-505 0 0,5-22-104 0 0,-106 422 503 0 0,84-306-857 0 0,-14 182 1 0 0,38-260-477 0 0,3 65-1 0 0,1-102-76 0 0,1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,1 0 0 0 0,1 0 0 0 0,12 26 0 0 0,-1-14-3169 0 0,-15-25 3315 0 0,8 6-1126 0 0,38 14-262 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1267.92">4758 1132 12883 0 0,'-5'-3'2616'0'0,"5"0"-2216"0"0,6-1-88 0 0,8-1-840 0 0,8-1 296 0 0,8 0 32 0 0,4 4 64 0 0,3 0 72 0 0,2 2-696 0 0,-2 4-448 0 0,-3 5-160 0 0,-2 3-1577 0 0,15 23-5817 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1424.51">4978 1968 13067 0 0,'0'-1'3056'0'0,"7"-4"-2904"0"0,10-7-184 0 0,8-7 24 0 0,12-8-16 0 0,11-3 233 0 0,5-4-185 0 0,10-1-72 0 0,5-1-73 0 0,2 0-575 0 0,2 3-1560 0 0,-5 1-1361 0 0,-9 0-248 0 0,-9 6 3913 0 0,-15-1-2992 0 0,-9 3 7 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1582.74">5256 85 17324 0 0,'-21'5'640'0'0,"4"7"240"0"0,6 4-1064 0 0,8 9-184 0 0,5 6 8 0 0,7 5 0 0 0,4 1 272 0 0,3-3-1433 0 0,5 2-655 0 0,1 0-385 0 0,5-2-2408 0 0,37 17-1280 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1742.53">5763 6 14707 0 0,'-5'-3'1480'0'0,"0"0"-1191"0"0,2 3-265 0 0,3 5-185 0 0,3 5-295 0 0,2 7 336 0 0,0 12 32 0 0,3 12 72 0 0,2 3 16 0 0,2 4-1168 0 0,2-1-512 0 0,-2 1-345 0 0,4 0-2120 0 0,33 38-2488 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2074.75">6350 865 11562 0 0,'-12'49'543'0'0,"3"1"0"0"0,1 1 0 0 0,3-1 0 0 0,2 65 0 0 0,-2 18-338 0 0,-6-21-155 0 0,4-56-893 0 0,3 0 1 0 0,2 1-1 0 0,7 82 0 0 0,-4-133 386 0 0,4 26-1260 0 0,-4-31 1419 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,34 22-6895 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2204.23">6827 937 14699 0 0,'18'-20'1096'0'0,"10"-4"-800"0"0,12-6-72 0 0,14 0-151 0 0,8 1-25 0 0,13 2-32 0 0,1 3-56 0 0,7 3-41 0 0,5 2-599 0 0,-5 7-1664 0 0,-1 0-1137 0 0,-12 6-344 0 0,-8 3 3865 0 0,-13 0-3064 0 0,-9 2 15 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2454.67">7513 508 13435 0 0,'3'7'3695'0'0,"10"28"-4055"0"0,-8-14 456 0 0,-1-1-1 0 0,-1 1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,-1 0-1 0 0,-3 31 1 0 0,-27 126 389 0 0,26-157-452 0 0,-112 441 1144 0 0,-27-6-355 0 0,39-129-531 0 0,-41 70-756 0 0,26-152-6938 0 0,75-160-4968 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-158.07">22 699 11042 0 0,'1'-4'7362'0'0,"-23"-29"-7194"0"0,32 23-320 0 0,23 5-8 0 0,16 2 48 0 0,8 0 176 0 0,5 2-40 0 0,6-2 0 0 0,5 3 0 0 0,0 4-16 0 0,12 5-32 0 0,6-1-88 0 0,4 4-40 0 0,3 7-672 0 0,-9 8-2105 0 0,-8 11 1833 0 0,-8 13-5482 0 0,-8 1 9 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="385.2">1924 911 8258 0 0,'-1'-5'6196'0'0,"10"3"-5250"0"0,18 0-2167 0 0,-26 2 1396 0 0,331 7 299 0 0,-281 0-1423 0 0,61 14 0 0 0,-74-10-1584 0 0,1 1 1 0 0,43 21 0 0 0,-53-20 1055 0 0,40 25 0 0 0,-36-14-894 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:23.500"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">22 839 11098 0 0,'-3'-4'210'0'0,"0"0"0"0"0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 1-1 0 0,-2-8 1 0 0,3 9-196 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,1-1 0 0 0,17-11-27 0 0,0 1 0 0 0,1 0 1 0 0,1 2-1 0 0,30-13 0 0 0,94-27 69 0 0,-38 23-326 0 0,1 4 1 0 0,213-18-1 0 0,-164 35-3681 0 0,-114 8-205 0 0,100 16-232 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="329.86">2225 20 13459 0 0,'-9'-11'608'0'0,"2"5"-368"0"0,4 3-240 0 0,9 9-688 0 0,9 3 440 0 0,6 3 32 0 0,10 4 128 0 0,6 4 120 0 0,8 1 96 0 0,-2 2-64 0 0,4 4-16 0 0,2 3-720 0 0,-1 4-2481 0 0,3 2 2025 0 0,-11 4-3065 0 0,-6 3 8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="487.34">2386 722 13123 0 0,'0'-6'464'0'0,"1"1"-560"0"0,2 2-128 0 0,8 0-88 0 0,1 0 48 0 0,5 0 136 0 0,4 2 128 0 0,3 1-72 0 0,1 6-112 0 0,-4 4-3665 0 0,-4 4 2737 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="645.19">2007 1553 13763 0 0,'-11'-10'584'0'0,"5"-1"-568"0"0,8 1-112 0 0,14-5-128 0 0,11-7-80 0 0,17-11 184 0 0,16-7 120 0 0,10-6-16 0 0,6-2 136 0 0,10 0-136 0 0,3 1-128 0 0,6 1-112 0 0,7 0-1080 0 0,87-41-10627 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="914.04">3591 922 10154 0 0,'-7'-8'397'0'0,"2"1"-20"0"0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-5-13 0 0 0,8 18-367 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,2-1 0 0 0,13-9-58 0 0,1 0 0 0 0,1 1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 2 0 0 0,0 0 0 0 0,0 2 0 0 0,1 0 0 0 0,0 1 1 0 0,1 1-1 0 0,-1 1 0 0 0,0 1 0 0 0,1 1 0 0 0,0 1 0 0 0,35 4 0 0 0,-51-3 38 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,4 5 0 0 0,-5-3 73 0 0,1 0 0 0 0,-2 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-2 0 1 0 0,1 0-1 0 0,1 14 1 0 0,0 41 327 0 0,-2 1 1 0 0,-8 78-1 0 0,0-36-320 0 0,5 59-4 0 0,3-90-822 0 0,-3 0 0 0 0,-21 133-1 0 0,20-191-202 0 0,-1 0-1 0 0,-1 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-2 0-1 0 0,0-1 1 0 0,-11 15-1 0 0,0-6-2468 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1056.62">3629 1325 10826 0 0,'-1'-16'512'0'0,"2"1"545"0"0,7 2-1009 0 0,7-1-184 0 0,7 1 24 0 0,11 1-56 0 0,2 0 72 0 0,10 2 40 0 0,3 2-8 0 0,1 4-8 0 0,6 4-337 0 0,-9 1-2871 0 0,-1 7 2231 0 0,-11 4-2455 0 0,-6 0 15 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1231.86">3690 1809 10962 0 0,'-19'-8'1232'0'0,"11"5"-696"0"0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-7-6 0 0 0,13 9-521 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,2-2 1 0 0,31-26-305 0 0,-26 23 340 0 0,17-14-60 0 0,2 1 0 0 0,0 1-1 0 0,50-22 1 0 0,93-25-98 0 0,36-3-1647 0 0,102-41-7670 0 0,-226 77 5044 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1355.49">5072 659 13179 0 0,'-4'-7'464'0'0,"1"2"280"0"0,6 4-1016 0 0,10 4-264 0 0,11 1 104 0 0,18 5-120 0 0,10 2 104 0 0,74 12-11691 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1513.66">5413 1510 15763 0 0,'-10'-24'1689'0'0,"8"2"-985"0"0,10 0-24 0 0,21-5-336 0 0,16-5-288 0 0,19 0-128 0 0,9 1-24 0 0,7 4-32 0 0,3 4-56 0 0,13 4-1968 0 0,0-2-1905 0 0,-1 6-352 0 0,-7 1 4473 0 0,-6-7-4169 0 0,10-8 16 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:20.113"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3256 5504 9122 0 0,'-215'-11'4449'0'0,"-105"12"-3539"0"0,-82-2-601 0 0,-9-21-50 0 0,-5-28 77 0 0,307 29-183 0 0,-186-60 0 0 0,224 55-110 0 0,0-4-1 0 0,2-2 0 0 0,-92-59 1 0 0,113 57-42 0 0,2-2 1 0 0,1-2 0 0 0,2-1 0 0 0,1-3-1 0 0,3-1 1 0 0,1-2 0 0 0,3-2-1 0 0,-53-90 1 0 0,42 52-86 0 0,3-3 0 0 0,4-2 0 0 0,5-1-1 0 0,-35-140 1 0 0,50 150 2 0 0,4 0 0 0 0,3-1 0 0 0,4 0 0 0 0,3 0 0 0 0,4-1 0 0 0,3 1-1 0 0,4 0 1 0 0,4 0 0 0 0,4 0 0 0 0,2 1 0 0 0,55-154 0 0 0,-28 133 25 0 0,4 1 1 0 0,5 3 0 0 0,3 2-1 0 0,5 2 1 0 0,76-90 0 0 0,-25 55-137 0 0,4 4-1 0 0,213-177 1 0 0,-107 125-208 0 0,7 11 0 0 0,8 9 0 0 0,5 11-1 0 0,8 10 1 0 0,4 12 0 0 0,422-144 0 0 0,-182 111 295 0 0,682-125 1 0 0,-320 178 577 0 0,-599 94 21 0 0,347 30 0 0 0,-466-7-267 0 0,0 6 0 0 0,-2 7 1 0 0,-1 5-1 0 0,255 96 0 0 0,-305-91-152 0 0,-2 3 0 0 0,-1 4-1 0 0,-3 3 1 0 0,-1 4 0 0 0,-3 3 0 0 0,-2 3-1 0 0,-3 4 1 0 0,91 98 0 0 0,-96-80-41 0 0,-4 2 1 0 0,-3 3-1 0 0,-3 2 1 0 0,42 92 0 0 0,-25-21 46 0 0,80 248 0 0 0,-102-240-197 0 0,48 302 1 0 0,-81-338 12 0 0,-5 0 1 0 0,-6 1-1 0 0,-12 131 1 0 0,-2-185 145 0 0,-2 1 0 0 0,-4-2 1 0 0,-3 0-1 0 0,-3-1 0 0 0,-4-1 1 0 0,-3-1-1 0 0,-41 76 0 0 0,19-57 184 0 0,-3-3 1 0 0,-4-2-1 0 0,-4-2 0 0 0,-129 134 1 0 0,103-134-38 0 0,-3-5 1 0 0,-4-3 0 0 0,-3-5 0 0 0,-190 104 0 0 0,95-77-41 0 0,-366 128-1 0 0,345-159-253 0 0,-283 52-1 0 0,-228-18-1316 0 0,372-75-474 0 0,266-24 390 0 0,1-4 0 0 0,-95-14 0 0 0,72-7-2274 0 0,6-5-568 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="806.25">6186 5541 7666 0 0,'-22'15'546'0'0,"-2"-1"9"0"0,1 2 0 0 0,0 0 1 0 0,1 1-1 0 0,2 1 0 0 0,-1 2 0 0 0,2 0 0 0 0,-26 34 0 0 0,17-9-562 0 0,-41 86-1 0 0,-12 59 66 0 0,59-136-27 0 0,-66 185-223 0 0,73-191-663 0 0,3 0 1 0 0,2 1-1 0 0,-5 54 1 0 0,16-51-1699 0 0,-1-50 2324 0 0,0 0 1 0 0,0 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,3 2 0 0 0,9 1-1990 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="979.63">6235 5355 12443 0 0,'7'-3'46'0'0,"1"-1"0"0"0,-1 1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,14 2 0 0 0,9 3 122 0 0,-1 1-1 0 0,32 10 0 0 0,-18-4-3 0 0,188 40 264 0 0,-93-23-1141 0 0,137 47 0 0 0,-216-55-1482 0 0,-26-6-2743 0 0,61 41-633 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1171.56">6207 5596 16700 0 0,'-2'8'-2'0'0,"0"-1"1"0"0,0 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,2 9-1 0 0,-1-7 8 0 0,7 60 44 0 0,2 0 0 0 0,4-1 0 0 0,3-1 0 0 0,3 0 0 0 0,35 79 1 0 0,9-3-215 0 0,104 168 0 0 0,78 54-6694 0 0,-36-60-42 0 0,-170-237 4001 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2297.03">7828 6722 6553 0 0,'-13'-19'560'0'0,"5"8"-28"0"0,0 0-1 0 0,1-1 0 0 0,0-1 1 0 0,-8-19-1 0 0,14 29-468 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,3-3 0 0 0,15-13 12 0 0,1 0-1 0 0,1 2 1 0 0,0 0-1 0 0,1 2 1 0 0,33-17-1 0 0,129-54 214 0 0,-123 61-252 0 0,2 2-1 0 0,1 3 1 0 0,0 3 0 0 0,1 3-1 0 0,1 2 1 0 0,114-4 0 0 0,-103 14 23 0 0,1 4 0 0 0,141 20 0 0 0,-184-15-137 0 0,0 1-1 0 0,-1 2 1 0 0,0 1 0 0 0,-1 2 0 0 0,0 2 0 0 0,-1 0-1 0 0,0 3 1 0 0,38 26 0 0 0,-50-29-238 0 0,0 1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 2 1 0 0,26 32-1 0 0,-40-46 276 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-2 0 1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,-4 5 0 0 0,-4 4 65 0 0,0-1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,-29 20 0 0 0,-121 61 158 0 0,137-79-159 0 0,-7 2 26 0 0,0-1 0 0 0,-1-1 0 0 0,0-2 0 0 0,-1-2 0 0 0,0-1 0 0 0,-1-2-1 0 0,0-1 1 0 0,0-2 0 0 0,0-2 0 0 0,0-1 0 0 0,-1-2 0 0 0,1-1 0 0 0,0-3 0 0 0,-46-10-1 0 0,62 9 122 0 0,1-1-1 0 0,0-2 0 0 0,1 1 1 0 0,0-2-1 0 0,0-1 0 0 0,1 0 1 0 0,0-2-1 0 0,-16-14 0 0 0,3 4 409 0 0,27 20-429 0 0,-5-3 363 0 0,15 6-784 0 0,-2 2 276 0 0,-1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,2 7 1 0 0,1 7 188 0 0,-1 0 0 0 0,2 25 0 0 0,-5-39-187 0 0,4 59 314 0 0,-3 0-1 0 0,-3 0 1 0 0,-2 0-1 0 0,-4 0 1 0 0,-21 88-1 0 0,0-41-172 0 0,-5-2 1 0 0,-54 116-1 0 0,42-128 4 0 0,-62 93 0 0 0,55-101-162 0 0,46-75-41 0 0,-23 44-165 0 0,28-52 67 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 6 0 0 0,0-10 27 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,2-1-1 0 0,33-17-2801 0 0,-20 8 2126 0 0,0-1 1 0 0,-1-1-1 0 0,19-20 1 0 0,15-18-1974 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2454.9">10021 7078 12459 0 0,'9'-30'368'0'0,"6"3"88"0"0,10 5-544 0 0,12 1-40 0 0,9 0 48 0 0,8 2-32 0 0,7 1 136 0 0,-2 5-128 0 0,1 5-528 0 0,-10 8-25 0 0,-8 8-2503 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2592.3">9802 7729 10322 0 0,'13'-13'272'0'0,"10"-3"-208"0"0,7-7-40 0 0,14-4 0 0 0,4-4 80 0 0,17 0-48 0 0,10 4 16 0 0,6 2-24 0 0,12 3-24 0 0,-1 1-328 0 0,-3 0-752 0 0,3 2 56 0 0,1-1-2521 0 0,95-21-1600 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2909.13">11270 6914 7866 0 0,'-45'-75'3853'0'0,"53"75"-3033"0"0,7 7-814 0 0,353 235 1332 0 0,-165-102-1003 0 0,18-4-142 0 0,36 24-1448 0 0,-219-132-400 0 0,-1 2 1 0 0,-2 1-1 0 0,-1 2 0 0 0,59 73 0 0 0,-30-23-3219 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3114.11">12405 6877 13347 0 0,'-11'-1'98'0'0,"-1"1"0"0"0,1 1 1 0 0,-1-1-1 0 0,1 2 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 1 0 0,0 1-1 0 0,0-1 0 0 0,-9 11 0 0 0,-15 20-85 0 0,1 0-1 0 0,-53 85 1 0 0,-38 98 67 0 0,34-56 6 0 0,-50 57-20 0 0,-30 53-1776 0 0,164-266 1322 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-3 13 0 0 0,6-20 164 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,2 5 0 0 0,16 16-3002 0 0,-4-13 660 0 0,53 14 243 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:33.265"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1064 1 9978 0 0,'-80'77'320'0'0,"-13"17"1801"0"0,59-55-3266 0 0,-3 13-695 0 0,-6 0-344 0 0,-3-2-137 0 0,-2 2 2337 0 0,-2 0-2488 0 0,-2-5 7 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="159.81">33 856 12923 0 0,'6'-3'-340'0'0,"201"-82"1355"0"0,-43 14-706 0 0,206-65-814 0 0,-135 54-3758 0 0,-194 71-88 0 0,90-14-429 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="381.49">0 1357 16331 0 0,'1'1'3'0'0,"-1"0"-1"0"0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 5 0 0,26 16 14 0 0,1-2-1 0 0,0-1 1 0 0,1-2 0 0 0,0-1 0 0 0,1 0-1 0 0,0-3 1 0 0,1 0 0 0 0,39 2 0 0 0,13-3-602 0 0,154-11 0 0 0,-211 3 296 0 0,109-3-2959 0 0,-112 5 1736 0 0,0 2-1 0 0,0 0 0 0 0,39 9 1 0 0,-29 2-1290 0 0,-5 2-278 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="778.95">110 1463 7626 0 0,'0'-4'232'0'0,"-1"-1"1"0"0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,4-3-1 0 0,8-8-277 0 0,1 0 0 0 0,1 2 0 0 0,23-15-1 0 0,-11 7 743 0 0,31-20-222 0 0,2 1 0 0 0,2 4 0 0 0,117-49 1 0 0,-67 42-294 0 0,177-41 1 0 0,-96 47-172 0 0,-170 34-262 0 0,0 1-1 0 0,0 1 1 0 0,0 2-1 0 0,0 0 1 0 0,47 10-1 0 0,-66-10 134 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,8 5 0 0 0,-12-7 85 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,-1 1-1 0 0,0 1 1 0 0,-13 15-180 0 0,0-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1-1-1 0 0,-1 0 0 0 0,-1-2 1 0 0,0 0-1 0 0,-1-1 1 0 0,-32 15-1 0 0,-19 4 110 0 0,-109 32 1 0 0,154-55 79 0 0,-32 11 44 0 0,0-3 1 0 0,-92 14 0 0 0,134-28-6 0 0,0-1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0-2 0 0 0,0 0-1 0 0,0 0 1 0 0,0-2-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,0-1 0 0 0,1-1-1 0 0,-24-14 1 0 0,32 17-23 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,5-15 0 0 0,-1 7 141 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 1 0 0,2 0-1 0 0,-1 1 0 0 0,2-1 0 0 0,0 2 0 0 0,0-1 0 0 0,1 2 1 0 0,25-22-1 0 0,-30 28-30 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 2 1 0 0,14-4-1 0 0,-18 5-67 0 0,0 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,4 7 0 0 0,3 4 135 0 0,-1 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,2 24 1 0 0,0 17 75 0 0,-2 90-1 0 0,-4-111-251 0 0,-8 266-632 0 0,5-209-2494 0 0,0 8-3634 0 0,0-11 1872 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="954.39">417 2025 5281 0 0,'-21'-17'5271'0'0,"21"15"-4942"0"0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1-2 0 0 0,1 1-297 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,3-2-1 0 0,8-12-10 0 0,143-162 418 0 0,-130 153-1367 0 0,1 1 1 0 0,1 1-1 0 0,1 1 1 0 0,45-26-1 0 0,-68 46 148 0 0,-1 0-1 0 0,1 0 1 0 0,1 0-1 0 0,10-2 0 0 0,-15 4 622 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,1 2 0 0 0,8 9-1717 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1113.66">548 2308 392 0 0,'-24'28'1009'0'0,"15"-18"102"0"0,1 0 1 0 0,0 0-1 0 0,-11 19 1 0 0,44-35 1476 0 0,7-12-1934 0 0,-1-1 0 0 0,-1-1-1 0 0,46-42 1 0 0,-1 2-239 0 0,191-134 383 0 0,-80 74-4270 0 0,-33 28-1597 0 0,-85 49 1355 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1415.58">1494 1188 14715 0 0,'14'-19'25'0'0,"2"0"-1"0"0,0 1 0 0 0,1 1 1 0 0,0 0-1 0 0,1 1 1 0 0,1 1-1 0 0,1 1 0 0 0,38-20 1 0 0,-6 7 12 0 0,1 3 0 0 0,80-25 0 0 0,-113 42-85 0 0,0 1 0 0 0,1 1 1 0 0,0 2-1 0 0,0-1 0 0 0,0 2 0 0 0,0 1 1 0 0,42 3-1 0 0,-54-1-7 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 1 0 0 0,8 13 0 0 0,-5-4-38 0 0,-1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-4 25 1 0 0,-4 4-128 0 0,-1 0 0 0 0,-3-1 0 0 0,-37 90 0 0 0,36-102 329 0 0,-3 0 1 0 0,-1-1-1 0 0,-1-1 1 0 0,-2-1-1 0 0,-1-1 1 0 0,-47 52-1 0 0,57-72-206 0 0,0 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0-1 0 0 0,-18 7 1 0 0,21-11-329 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1-1 0 0 0,-1 0-1 0 0,-14-4 1 0 0,16 2-130 0 0,-1 0 0 0 0,1-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0-1-1 0 0,-14-12 0 0 0,22 18 546 0 0,-1 0-94 0 0,-8-15-406 0 0,-22-55-92 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1543.21">1678 1108 1480 0 0,'11'-33'264'0'0,"27"-71"2886"0"0,-32 90-2103 0 0,1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 1 0 0,16-10 2403 0 0,-24 23-3409 0 0,2 13 754 0 0,0 14-381 0 0,-2-27-383 0 0,-1 86 721 0 0,-3 0-1 0 0,-18 91 0 0 0,-46 167-630 0 0,54-279-188 0 0,-73 390-3448 0 0,68-314-33 0 0,6-27-3642 0 0,3-23 4267 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1924.46">3213 406 14563 0 0,'-21'3'-32'0'0,"-1"1"0"0"0,1 1-1 0 0,-1 1 1 0 0,2 1 0 0 0,-1 1 0 0 0,1 1 0 0 0,0 1-1 0 0,1 0 1 0 0,0 2 0 0 0,0 0 0 0 0,2 1 0 0 0,-27 24-1 0 0,-66 43-550 0 0,58-45 357 0 0,51-35 191 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 2 0 0 0,5 10 178 0 0,10 22-74 0 0,-1 2 0 0 0,-2 0-1 0 0,-2 0 1 0 0,-1 1 0 0 0,-2 1 0 0 0,7 57 0 0 0,3 239 2087 0 0,-14-166-1180 0 0,-4-132-970 0 0,13 136 392 0 0,-11-149-714 0 0,1 0 1 0 0,2-1 0 0 0,0 0-1 0 0,1 0 1 0 0,14 28 0 0 0,-5-23-3382 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2177.77">2873 1069 13235 0 0,'-1'-1'56'0'0,"1"1"-1"0"0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,2 0 0 0 0,32-22-695 0 0,-24 16 869 0 0,29-21-198 0 0,1 2 0 0 0,85-41 1 0 0,-102 57-55 0 0,1 0 1 0 0,-1 2 0 0 0,1 2 0 0 0,1 0-1 0 0,-1 1 1 0 0,1 1 0 0 0,37-1 0 0 0,-55 5 8 0 0,-1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,8 7 1 0 0,-8-4 17 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,3 13 1 0 0,2 12 21 0 0,-2 0 0 0 0,-1 1 0 0 0,-2 0 0 0 0,-1 56 0 0 0,-9 163-2086 0 0,3-216 145 0 0,-2-1 0 0 0,-2 0 0 0 0,-1-1 0 0 0,-23 65 0 0 0,15-66-1143 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2321.56">3032 1466 12707 0 0,'-9'-13'2656'0'0,"9"4"-2984"0"0,12-3-232 0 0,7-5 112 0 0,10-3-72 0 0,6-4 432 0 0,4 0-656 0 0,1-1-88 0 0,0 4-241 0 0,-4 3-495 0 0,26 0-7626 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2463.42">3199 1738 11610 0 0,'-26'3'1529'0'0,"7"0"-1585"0"0,4 0-240 0 0,8-3-256 0 0,10-12-1993 0 0,4-1 865 0 0,29-33-6322 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2797.62">3996 844 15027 0 0,'-14'8'273'0'0,"1"0"0"0"0,0 1-1 0 0,0 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,-11 15-1 0 0,-7 12-692 0 0,-25 42 0 0 0,32-45 344 0 0,23-34-15 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 1 1 0 0,0-1 46 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,3-1 0 0 0,58-18 415 0 0,-61 18-407 0 0,172-78 500 0 0,27-9-122 0 0,-176 79-252 0 0,1 2 0 0 0,0 1 0 0 0,0 1 0 0 0,0 1 0 0 0,1 2 0 0 0,42 0 0 0 0,-50 2-43 0 0,1 2 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 1 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1-1 0 0,26 15 1 0 0,-35-16-34 0 0,0 1 0 0 0,0-1 0 0 0,0 2-1 0 0,0-1 1 0 0,-1 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-2 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,2 15-1 0 0,-2 1 55 0 0,-1 0 0 0 0,-1 0 0 0 0,-2 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-1-1-1 0 0,-13 36 1 0 0,2-15-9 0 0,-2-2-1 0 0,-2 0 1 0 0,-1-1 0 0 0,-37 54-1 0 0,41-74-345 0 0,-1 0 0 0 0,-1 0 0 0 0,-1-2 0 0 0,-36 31 0 0 0,40-40-815 0 0,-1 0 0 0 0,-32 17 0 0 0,36-23-291 0 0,0-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-22 5 0 0 0,-3-5-3259 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2924.74">4125 1417 11010 0 0,'-25'-3'5559'0'0,"29"5"-5590"0"0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,8 0-1 0 0,19 3 109 0 0,2 7-7 0 0,-1 1 0 0 0,40 20 0 0 0,4 2 13 0 0,132 35-692 0 0,-102-40-5890 0 0,-73-19 2962 0 0,71 20-2452 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:44.742"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">56 19 4833 0 0,'-9'-2'2233'0'0,"-37"-3"-1245"0"0,76 16 947 0 0,24-3-1400 0 0,0-2 1 0 0,0-3-1 0 0,94-6 1 0 0,-74 0-440 0 0,357-12 53 0 0,416-4 135 0 0,-450 24-77 0 0,-22-1-2038 0 0,-111-3-6338 0 0,-188-1 5310 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:45.863"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 151 9194 0 0,'50'-45'4356'0'0,"2"7"-3388"0"0,-38 30-1033 0 0,-1 1 1 0 0,1 0 0 0 0,0 1-1 0 0,0 1 1 0 0,1 0-1 0 0,23-4 1 0 0,48-2-49 0 0,-1 4 0 0 0,122 5 0 0 0,-87 3 100 0 0,5-2 2 0 0,366 1-609 0 0,-2 35-1632 0 0,43 26-785 0 0,-149-32-3787 0 0,-263-22 5861 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink8.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:46.718"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 45 12459 0 0,'0'-2'87'0'0,"0"0"19"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,2-4 0 0 0,-1 6-133 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,3 1-1 0 0,334-6-69 0 0,-15-1 492 0 0,429 33-331 0 0,-336-10-1717 0 0,1-6-3712 0 0,-130-4 1837 0 0,-138-5 373 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink9.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:50.792"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 222 7690 0 0,'8'-6'505'0'0,"0"0"0"0"0,1 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,17-4 0 0 0,75-10-1258 0 0,-66 14 1123 0 0,1427-124 24 0 0,-1347 124-671 0 0,1026-22-4509 0 0,-1081 27 1640 0 0,146 3-377 0 0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1011,12 +2507,12 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="3:15">
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="D10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
       <c r="H10" t="s">
         <v>2</v>
       </c>
@@ -1049,10 +2545,10 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="3:15">
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="14"/>
+      <c r="D16" s="16"/>
       <c r="I16" s="2"/>
       <c r="O16" s="2"/>
     </row>
@@ -1060,7 +2556,7 @@
       <c r="C17" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="15"/>
+      <c r="D17" s="18"/>
       <c r="I17" s="2"/>
       <c r="O17" s="2"/>
     </row>
@@ -1075,50 +2571,50 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="3:15">
-      <c r="C19" s="18"/>
-      <c r="D19" s="16"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
       <c r="I19" s="2"/>
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="3:15">
-      <c r="C20" s="18"/>
-      <c r="D20" s="16"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="13"/>
       <c r="I20" s="2"/>
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="3:15">
-      <c r="C21" s="18"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
       <c r="I21" s="2"/>
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="3:15">
-      <c r="C22" s="18"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="13"/>
       <c r="I22" s="2"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="3:15">
-      <c r="C23" s="18"/>
-      <c r="D23" s="16"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="13"/>
       <c r="I23" s="2"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="3:15">
-      <c r="C24" s="18"/>
-      <c r="D24" s="16"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="13"/>
       <c r="I24" s="2"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="3:15">
-      <c r="C25" s="18"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="13"/>
       <c r="I25" s="2"/>
       <c r="O25" s="2"/>
     </row>
     <row r="26" spans="3:15">
       <c r="C26" s="3"/>
-      <c r="D26" s="16"/>
+      <c r="D26" s="13"/>
       <c r="I26" s="2"/>
       <c r="O26" s="2"/>
     </row>
@@ -1244,4 +2740,93 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A58E9B-0E21-46D4-B35A-F135C635A677}">
+  <dimension ref="A2:X35"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="6:9">
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="6:9">
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="6:9">
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="9:9">
+      <c r="I33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="9:9">
+      <c r="I34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="9:9">
+      <c r="I35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/設計書/設計書.xlsx
+++ b/設計書/設計書.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\computer-visualizer\設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE3F695-8C92-4689-B641-56E2FD0EE948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208EB023-DF3A-470C-B6A0-0942082CEC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="概要" sheetId="1" r:id="rId1"/>
+    <sheet name="Front" sheetId="3" r:id="rId2"/>
+    <sheet name="具体的" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>スタック</t>
     <phoneticPr fontId="1"/>
@@ -44,6 +46,68 @@
   </si>
   <si>
     <t>← num</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーサー（Parser）とは、コンピュータの世界では文章やコードなどの構造化されていないデータを解析し、プログラムが理解できるデータ構造に変換する仕組み（構文解析器）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AST（抽象構文木）とは、コードを「コンピュータが扱いやすい木構造」にしたもの</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：JS</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・解析対象言語…C#</t>
+    <rPh sb="1" eb="5">
+      <t>カイセキタイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・C#AST…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・C#パーサー…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・エディタ…Monaco</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Roslynは、そもそもC#のコンパイラ基盤そのものなので、C#コードを解析してSyntax Tree（構文木）を作る機能を持っている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>構文としての条件をそのコードが満たしているか(例えば「inti t = #」みたいな構文としての条件を満たしていないコードがかかれたら何も起こらないという仕様にしたい)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→これもRoslynが判定して(シンタックスerrorだしてくれる)→そのままreturn</t>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面分割</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンカツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -215,20 +279,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -686,7 +750,1587 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>58209</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>146345</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>375285</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>227953</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="21" name="インク 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E8A0C3-6572-E4CD-6CC3-1DD914F83377}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="730080" y="3128797"/>
+            <a:ext cx="3004560" cy="2834640"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="インク 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E8A0C3-6572-E4CD-6CC3-1DD914F83377}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="694084" y="3093157"/>
+              <a:ext cx="3076191" cy="2906280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>582285</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>137891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>8610</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>34074</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="37" name="インク 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{100C73D3-7FA3-6EE7-1189-2E4CEB3AE9E2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3941640" y="5185117"/>
+            <a:ext cx="2785680" cy="1043280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="37" name="インク 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{100C73D3-7FA3-6EE7-1189-2E4CEB3AE9E2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3906000" y="5149117"/>
+              <a:ext cx="2857320" cy="1114920"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>432219</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>208228</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>24615</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>208650</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="57" name="インク 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A0C6DEA-2A19-6F1A-DABE-4D70D6ADEE08}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7822800" y="4108357"/>
+            <a:ext cx="2279880" cy="688680"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="57" name="インク 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A0C6DEA-2A19-6F1A-DABE-4D70D6ADEE08}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7786800" y="4072376"/>
+              <a:ext cx="2351520" cy="760283"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>245796</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>122102</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>77619</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>166530</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="58" name="インク 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC02053-C5F2-4F6A-B329-F00BD948FE61}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2933280" y="1728037"/>
+            <a:ext cx="4534920" cy="3026880"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="58" name="インク 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC02053-C5F2-4F6A-B329-F00BD948FE61}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2897640" y="1692397"/>
+              <a:ext cx="4606560" cy="3098520"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>180690</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>111971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>580068</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>87454</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="73" name="インク 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFE15520-D428-F32D-AF0D-ED3E340DA8A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6899400" y="5159197"/>
+            <a:ext cx="1743120" cy="893160"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="73" name="インク 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFE15520-D428-F32D-AF0D-ED3E340DA8A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6863393" y="5123543"/>
+              <a:ext cx="1814775" cy="964829"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>544095</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>181985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>210154</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>196745</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="74" name="インク 73">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A14C5D46-CD11-637F-2167-20FE3C53C5EA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10622160" y="3164437"/>
+            <a:ext cx="1009800" cy="14760"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="74" name="インク 73">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A14C5D46-CD11-637F-2167-20FE3C53C5EA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10586520" y="3128437"/>
+              <a:ext cx="1081440" cy="86400"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>550215</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>237154</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>120587</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="75" name="インク 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70857AFB-0CD4-C3EC-DF6B-B9535BF82F96}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10628280" y="3507517"/>
+            <a:ext cx="1030680" cy="54360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="75" name="インク 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70857AFB-0CD4-C3EC-DF6B-B9535BF82F96}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10592280" y="3471877"/>
+              <a:ext cx="1102320" cy="126000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>517095</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>115708</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>150754</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>139108</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="76" name="インク 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDB16D33-EAF4-3A9B-1FA3-1CB9E14010E8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10595160" y="4015837"/>
+            <a:ext cx="977400" cy="23400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="76" name="インク 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDB16D33-EAF4-3A9B-1FA3-1CB9E14010E8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10559520" y="3979837"/>
+              <a:ext cx="1049040" cy="95040"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>432135</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>39549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>246514</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>119829</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="77" name="インク 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51A8E941-4835-817C-EBBB-1D37F7FBD7D9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10510200" y="4398517"/>
+            <a:ext cx="1158120" cy="80280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="77" name="インク 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51A8E941-4835-817C-EBBB-1D37F7FBD7D9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10474560" y="4362517"/>
+              <a:ext cx="1229760" cy="151920"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>387357</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>168380</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>603634</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>153645</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="86" name="インク 85">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EFD229D-2691-65B0-756B-8B7D379EDA04}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9121680" y="1315477"/>
+            <a:ext cx="2903760" cy="1591200"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="86" name="インク 85">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EFD229D-2691-65B0-756B-8B7D379EDA04}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9086040" y="1279477"/>
+              <a:ext cx="2975400" cy="1662840"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434893</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>76422</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11B28754-3FA5-751A-0102-6FCD827B6915}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="83820" y="487680"/>
+          <a:ext cx="6386113" cy="2560542"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>312658</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>91708</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1E50048-DEDA-D455-2950-8090B27B2EFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="251460" y="198120"/>
+          <a:ext cx="2743438" cy="3093988"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>381252</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>221142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80592393-6936-FA6B-FB20-2EFE956898C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2164080" y="1325880"/>
+          <a:ext cx="2911092" cy="1867062"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>560012</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>328036</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>15763</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A36EFC1-353B-8665-4C0F-DAB0D12B22FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5253932" y="1165860"/>
+          <a:ext cx="3120824" cy="4336303"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>640503</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>106938</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2F7262-9B89-25C6-B747-47A476E10754}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="457200" y="6050280"/>
+          <a:ext cx="4877223" cy="2972058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E083EC-60A9-1D88-D8D2-3F2FCD0AC144}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="9349740"/>
+          <a:ext cx="4206240" cy="4023360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Angualr</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>↓</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>エディタの入力値取得</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>一文</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>して</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>JSON</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>化</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>↓</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>API</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Roslyn</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>でパース</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>AST</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Syntax Tree</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>）作成</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>「フロントが描画するために必要な情報」をまとめた</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>SimulationState</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>オブジェクト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>画面用の状態データ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>JSON</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Angular</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>描画</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>503403</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>69026</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{028D250F-2184-5D54-56AC-A9E76BA2AC4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="289560" y="13891260"/>
+          <a:ext cx="5578323" cy="5151566"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>251871</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>8123</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB6612E-3890-0D3B-1753-D00336ED18DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6240780" y="13860780"/>
+          <a:ext cx="4740051" cy="5806943"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:09.334"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4419 7735 11979 0 0,'-116'45'4259'0'0,"-91"28"-3504"0"0,182-67-653 0 0,-1-1-1 0 0,1-1 1 0 0,-1-1-1 0 0,0-1 1 0 0,0-1-1 0 0,-42-5 1 0 0,-461-49 1450 0 0,-157-29-389 0 0,515 53-618 0 0,-296-91 1 0 0,375 88-446 0 0,2-3 1 0 0,1-5-1 0 0,2-3 1 0 0,-138-93 0 0 0,142 71-72 0 0,-137-139 1 0 0,131 117-5 0 0,17 18-33 0 0,3-4 0 0 0,3-2 0 0 0,3-3 0 0 0,-53-87 0 0 0,-4-40-54 0 0,9-6 0 0 0,-94-251 0 0 0,157 332 35 0 0,6-1 1 0 0,5-3-1 0 0,7-1 0 0 0,5-1 0 0 0,-10-210 0 0 0,28 63-57 0 0,13-1-1 0 0,43-286 1 0 0,-29 453 30 0 0,5 0 0 0 0,77-218 0 0 0,134-204-181 0 0,-172 417 144 0 0,6 4 0 0 0,4 3 0 0 0,129-152 0 0 0,315-272-313 0 0,-381 418 402 0 0,247-170 0 0 0,190-47-2 0 0,-434 270-33 0 0,3 6-1 0 0,253-73 0 0 0,-187 82-35 0 0,298-37 1 0 0,-361 74-5 0 0,1 6 1 0 0,0 7 0 0 0,1 6 0 0 0,-1 6-1 0 0,194 38 1 0 0,-237-26 118 0 0,-1 6 0 0 0,-2 3 0 0 0,-1 5 1 0 0,-1 5-1 0 0,-2 3 0 0 0,-3 5 0 0 0,-1 4 0 0 0,99 74 0 0 0,188 186 222 0 0,-308-244-189 0 0,-4 4 1 0 0,115 155 0 0 0,129 274 128 0 0,-255-392-156 0 0,-5 2 0 0 0,66 211 0 0 0,-78-171 10 0 0,-8 2 0 0 0,-5 1 1 0 0,-8 1-1 0 0,-6 1 1 0 0,-8 1-1 0 0,-6-1 0 0 0,-40 297 1 0 0,17-323 18 0 0,-5-1 0 0 0,-87 234 0 0 0,50-202 94 0 0,-149 259 0 0 0,-7-60 58 0 0,146-251-115 0 0,-104 117-1 0 0,-2-27 169 0 0,-360 304 0 0 0,177-221-73 0 0,259-209-127 0 0,-180 94 1 0 0,122-88-483 0 0,-336 114-1 0 0,386-159-951 0 0,-2-4-1 0 0,-1-5 1 0 0,-220 16-1 0 0,180-36-5878 0 0,-168-16 0 0 0,247 3 4692 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1568.07">6450 5639 7618 0 0,'-3'-10'3906'0'0,"4"9"-3834"0"0,-1 1-71 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,5 44 283 0 0,-2 1 0 0 0,-3-1 1 0 0,-5 57-1 0 0,2-57-182 0 0,-28 344 202 0 0,-96 459 1 0 0,117-805-509 0 0,3-12-694 0 0,1 1 0 0 0,1 0 1 0 0,0 57-1 0 0,8-71-1514 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1819.2">6515 5556 11779 0 0,'0'-1'62'0'0,"-1"0"0"0"0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,33-14-445 0 0,-25 11 598 0 0,24-7-115 0 0,1 1 0 0 0,-1 2 0 0 0,1 1 0 0 0,1 2 0 0 0,-1 2 0 0 0,56 0-1 0 0,216 29 24 0 0,-295-25-110 0 0,374 71-4666 0 0,-380-71 4385 0 0,42 13-4311 0 0,96 39-415 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2119.47">6647 5492 14227 0 0,'0'0'17'0'0,"0"0"-1"0"0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,15-4-61 0 0,24 1-257 0 0,-17 3 321 0 0,-1 1 0 0 0,0 0 0 0 0,1 2 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 2 0 0 0,-1 0 0 0 0,20 10 0 0 0,-14-3 7 0 0,0 1 1 0 0,-2 1-1 0 0,0 1 0 0 0,-1 1 0 0 0,39 38 0 0 0,-23-13 13 0 0,-1 2 0 0 0,35 53 0 0 0,53 102 32 0 0,-114-180-66 0 0,141 235 78 0 0,98 162-2183 0 0,-78-144-2921 0 0,-35-76 206 0 0,-111-161 3685 0 0,-21-27 818 0 0,-1-2 90 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,13 11 1 0 0,138 118-797 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink10.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:53.503"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3472 602 8442 0 0,'6'43'2829'0'0,"3"20"-3271"0"0,-12 122 674 0 0,-31 205-1 0 0,15-209-189 0 0,-80 620 41 0 0,5-42 44 0 0,74-448-275 0 0,20-248 104 0 0,2 0 0 0 0,22 118 0 0 0,-22-170 43 0 0,1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,10 17 0 0 0,-12-23 7 0 0,0-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,9 4 0 0 0,19 0 150 0 0,0 0 0 0 0,0-3 0 0 0,0 0-1 0 0,0-2 1 0 0,45-5 0 0 0,-42 2-77 0 0,731 4 587 0 0,0 33-523 0 0,-214-8-269 0 0,1366 6 45 0 0,-1700-41-865 0 0,-79-7-4227 0 0,-126 12 1822 0 0,21-8-172 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="490.51">3606 391 11707 0 0,'-7'-13'-40'0'0,"5"9"6"0"0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1-5 0 0 0,2 9-24 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,3 0 0 0 0,3-2-94 0 0,342-90-89 0 0,117-27 499 0 0,-326 90-168 0 0,195-15 0 0 0,-41 31-135 0 0,455 40 0 0 0,-246 41-71 0 0,-7 30 306 0 0,-432-84-110 0 0,-17-4 244 0 0,-1 2 1 0 0,91 35-1 0 0,-117-37-209 0 0,0 1 0 0 0,0 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 2-1 0 0,-1 0 1 0 0,0 1 0 0 0,18 22 0 0 0,-11-7-59 0 0,-2 1 0 0 0,-2 1 0 0 0,-1 2 0 0 0,-1 0 0 0 0,-2 0 0 0 0,-1 2 0 0 0,-2 0 0 0 0,-2 1 0 0 0,-1 0 0 0 0,9 67 0 0 0,-7 0 163 0 0,-6 0 1 0 0,-9 194-1 0 0,-51 250 356 0 0,-31 0-435 0 0,25-181-260 0 0,-7 99-290 0 0,-73 447-730 0 0,132-877 970 0 0,-12 59-2327 0 0,16-85 962 0 0,0 0 0 0 0,-1 0 0 0 0,-7 12 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1443.25">82 1535 8514 0 0,'79'-71'4148'0'0,"-56"53"-4142"0"0,0 1 0 0 0,0 1 0 0 0,2 1 0 0 0,0 1 0 0 0,0 1 0 0 0,43-14 0 0 0,111-24-170 0 0,-156 46-13 0 0,1 1 0 0 0,0 1 0 0 0,0 1-1 0 0,0 2 1 0 0,42 3 0 0 0,-61-3 124 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,4 7-1 0 0,-4-4 41 0 0,0 1 0 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 10 0 0 0,-3 5 38 0 0,0 1 1 0 0,-2-1-1 0 0,-1 0 0 0 0,0-1 0 0 0,-16 32 0 0 0,4-16 8 0 0,-1-1-1 0 0,-32 45 0 0 0,30-54 39 0 0,0-1 0 0 0,-2-1 1 0 0,-1-1-1 0 0,-44 35 0 0 0,23-27 28 0 0,-1-2 0 0 0,-58 30-1 0 0,65-40 63 0 0,-1-2-1 0 0,-46 15 1 0 0,87-34-260 0 0,1 5-8 0 0,1 0 0 0 0,-1 0 0 0 0,2 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,2-1 0 0 0,-1 1 0 0 0,5 4-1 0 0,9 19 140 0 0,-10-12 20 0 0,0 1-1 0 0,-1 0 1 0 0,-1-1 0 0 0,0 2-1 0 0,-1-1 1 0 0,-1 0 0 0 0,-1 1-1 0 0,-1 0 1 0 0,-2 30 0 0 0,-4-2 41 0 0,-2-1 1 0 0,-22 77-1 0 0,-21 89 150 0 0,-41 132-68 0 0,26-134-3531 0 0,59-192-596 0 0,0 28-388 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1632.32">804 2021 17588 0 0,'0'-16'488'0'0,"3"4"80"0"0,0 3-968 0 0,12 8-72 0 0,7-5 32 0 0,17 1-8 0 0,14 1 176 0 0,11-2-569 0 0,2-2-415 0 0,1 2-112 0 0,-3 1-1425 0 0,44 3-7553 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1805.67">1430 2668 16347 0 0,'21'-16'2537'0'0,"9"-5"-2489"0"0,11-3 32 0 0,19-2-176 0 0,11 0-256 0 0,14 4-336 0 0,1 0-104 0 0,-2-1-81 0 0,-4 0-335 0 0,-4-4-1384 0 0,-6 2-1305 0 0,3 1-272 0 0,1 0 4217 0 0,-7 3-2249 0 0,-5 0 17 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1979.88">2219 1889 16283 0 0,'0'0'1761'0'0,"5"7"-1913"0"0,10 13-120 0 0,12 15-320 0 0,9 15 704 0 0,8 16 24 0 0,3 4 0 0 0,0-1-16 0 0,1-2-120 0 0,-1-9-872 0 0,-1-3-513 0 0,-2-3-159 0 0,-3-2-1561 0 0,38 32-7513 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2170.56">2831 1547 16692 0 0,'-5'2'23'0'0,"0"0"-1"0"0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-5 7 0 0 0,-3 7-142 0 0,0 2 0 0 0,-9 21 0 0 0,9-18 171 0 0,-79 170-91 0 0,20-37-655 0 0,-127 205 0 0 0,146-284-254 0 0,-109 183-7764 0 0,73-106 5621 0 0,45-90 569 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:15.059"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">179 2126 15707 0 0,'-35'-2'3609'0'0,"6"2"-2265"0"0,11 0-727 0 0,13-1-177 0 0,27-5-1825 0 0,12-4 825 0 0,17-5 0 0 0,10-6 632 0 0,10-4-256 0 0,3 1-416 0 0,8-2 32 0 0,7 3-1097 0 0,7 0-1391 0 0,-3 3 1920 0 0,-3 3-4906 0 0,-16 2 17 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="538.34">2071 1877 13547 0 0,'-89'3'5108'0'0,"175"-17"-5492"0"0,95-28 0 0 0,-25 5-1684 0 0,184-15-7195 0 0,-311 48 7677 0 0,45-6-3376 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="918.79">3794 728 9898 0 0,'-12'-6'2833'0'0,"14"1"-2257"0"0,9 5-1184 0 0,7-3 496 0 0,9-1 24 0 0,18-2 136 0 0,7-2-8 0 0,13-3-40 0 0,5-3 32 0 0,-3 4-40 0 0,-1-1-232 0 0,-7 4-2241 0 0,-4 2 1681 0 0,-7-2-3745 0 0,-8 0 8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1124.17">4371 548 2809 0 0,'-8'1'1442'0'0,"1"0"1"0"0,-1 1 0 0 0,1-1 0 0 0,-1 2 0 0 0,-12 5 0 0 0,14-5-1131 0 0,0 1 1 0 0,1-1 0 0 0,0 1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,1 0-1 0 0,-7 11 1 0 0,-11 24 197 0 0,1 1 0 0 0,-22 68 0 0 0,-16 92 126 0 0,48-163-505 0 0,5-22-104 0 0,-106 422 503 0 0,84-306-857 0 0,-14 182 1 0 0,38-260-477 0 0,3 65-1 0 0,1-102-76 0 0,1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,1 0 0 0 0,1 0 0 0 0,12 26 0 0 0,-1-14-3169 0 0,-15-25 3315 0 0,8 6-1126 0 0,38 14-262 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1267.92">4758 1132 12883 0 0,'-5'-3'2616'0'0,"5"0"-2216"0"0,6-1-88 0 0,8-1-840 0 0,8-1 296 0 0,8 0 32 0 0,4 4 64 0 0,3 0 72 0 0,2 2-696 0 0,-2 4-448 0 0,-3 5-160 0 0,-2 3-1577 0 0,15 23-5817 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1424.51">4978 1968 13067 0 0,'0'-1'3056'0'0,"7"-4"-2904"0"0,10-7-184 0 0,8-7 24 0 0,12-8-16 0 0,11-3 233 0 0,5-4-185 0 0,10-1-72 0 0,5-1-73 0 0,2 0-575 0 0,2 3-1560 0 0,-5 1-1361 0 0,-9 0-248 0 0,-9 6 3913 0 0,-15-1-2992 0 0,-9 3 7 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1582.74">5256 85 17324 0 0,'-21'5'640'0'0,"4"7"240"0"0,6 4-1064 0 0,8 9-184 0 0,5 6 8 0 0,7 5 0 0 0,4 1 272 0 0,3-3-1433 0 0,5 2-655 0 0,1 0-385 0 0,5-2-2408 0 0,37 17-1280 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1742.53">5763 6 14707 0 0,'-5'-3'1480'0'0,"0"0"-1191"0"0,2 3-265 0 0,3 5-185 0 0,3 5-295 0 0,2 7 336 0 0,0 12 32 0 0,3 12 72 0 0,2 3 16 0 0,2 4-1168 0 0,2-1-512 0 0,-2 1-345 0 0,4 0-2120 0 0,33 38-2488 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2074.75">6350 865 11562 0 0,'-12'49'543'0'0,"3"1"0"0"0,1 1 0 0 0,3-1 0 0 0,2 65 0 0 0,-2 18-338 0 0,-6-21-155 0 0,4-56-893 0 0,3 0 1 0 0,2 1-1 0 0,7 82 0 0 0,-4-133 386 0 0,4 26-1260 0 0,-4-31 1419 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,34 22-6895 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2204.23">6827 937 14699 0 0,'18'-20'1096'0'0,"10"-4"-800"0"0,12-6-72 0 0,14 0-151 0 0,8 1-25 0 0,13 2-32 0 0,1 3-56 0 0,7 3-41 0 0,5 2-599 0 0,-5 7-1664 0 0,-1 0-1137 0 0,-12 6-344 0 0,-8 3 3865 0 0,-13 0-3064 0 0,-9 2 15 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2454.67">7513 508 13435 0 0,'3'7'3695'0'0,"10"28"-4055"0"0,-8-14 456 0 0,-1-1-1 0 0,-1 1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,-1 0-1 0 0,-3 31 1 0 0,-27 126 389 0 0,26-157-452 0 0,-112 441 1144 0 0,-27-6-355 0 0,39-129-531 0 0,-41 70-756 0 0,26-152-6938 0 0,75-160-4968 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-158.07">22 699 11042 0 0,'1'-4'7362'0'0,"-23"-29"-7194"0"0,32 23-320 0 0,23 5-8 0 0,16 2 48 0 0,8 0 176 0 0,5 2-40 0 0,6-2 0 0 0,5 3 0 0 0,0 4-16 0 0,12 5-32 0 0,6-1-88 0 0,4 4-40 0 0,3 7-672 0 0,-9 8-2105 0 0,-8 11 1833 0 0,-8 13-5482 0 0,-8 1 9 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="385.2">1924 911 8258 0 0,'-1'-5'6196'0'0,"10"3"-5250"0"0,18 0-2167 0 0,-26 2 1396 0 0,331 7 299 0 0,-281 0-1423 0 0,61 14 0 0 0,-74-10-1584 0 0,1 1 1 0 0,43 21 0 0 0,-53-20 1055 0 0,40 25 0 0 0,-36-14-894 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:23.500"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">22 839 11098 0 0,'-3'-4'210'0'0,"0"0"0"0"0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 1-1 0 0,-2-8 1 0 0,3 9-196 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,1-1 0 0 0,17-11-27 0 0,0 1 0 0 0,1 0 1 0 0,1 2-1 0 0,30-13 0 0 0,94-27 69 0 0,-38 23-326 0 0,1 4 1 0 0,213-18-1 0 0,-164 35-3681 0 0,-114 8-205 0 0,100 16-232 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="329.86">2225 20 13459 0 0,'-9'-11'608'0'0,"2"5"-368"0"0,4 3-240 0 0,9 9-688 0 0,9 3 440 0 0,6 3 32 0 0,10 4 128 0 0,6 4 120 0 0,8 1 96 0 0,-2 2-64 0 0,4 4-16 0 0,2 3-720 0 0,-1 4-2481 0 0,3 2 2025 0 0,-11 4-3065 0 0,-6 3 8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="487.34">2386 722 13123 0 0,'0'-6'464'0'0,"1"1"-560"0"0,2 2-128 0 0,8 0-88 0 0,1 0 48 0 0,5 0 136 0 0,4 2 128 0 0,3 1-72 0 0,1 6-112 0 0,-4 4-3665 0 0,-4 4 2737 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="645.19">2007 1553 13763 0 0,'-11'-10'584'0'0,"5"-1"-568"0"0,8 1-112 0 0,14-5-128 0 0,11-7-80 0 0,17-11 184 0 0,16-7 120 0 0,10-6-16 0 0,6-2 136 0 0,10 0-136 0 0,3 1-128 0 0,6 1-112 0 0,7 0-1080 0 0,87-41-10627 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="914.04">3591 922 10154 0 0,'-7'-8'397'0'0,"2"1"-20"0"0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-5-13 0 0 0,8 18-367 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,2-1 0 0 0,13-9-58 0 0,1 0 0 0 0,1 1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 2 0 0 0,0 0 0 0 0,0 2 0 0 0,1 0 0 0 0,0 1 1 0 0,1 1-1 0 0,-1 1 0 0 0,0 1 0 0 0,1 1 0 0 0,0 1 0 0 0,35 4 0 0 0,-51-3 38 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,4 5 0 0 0,-5-3 73 0 0,1 0 0 0 0,-2 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-2 0 1 0 0,1 0-1 0 0,1 14 1 0 0,0 41 327 0 0,-2 1 1 0 0,-8 78-1 0 0,0-36-320 0 0,5 59-4 0 0,3-90-822 0 0,-3 0 0 0 0,-21 133-1 0 0,20-191-202 0 0,-1 0-1 0 0,-1 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-2 0-1 0 0,0-1 1 0 0,-11 15-1 0 0,0-6-2468 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1056.61">3629 1325 10826 0 0,'-1'-16'512'0'0,"2"1"545"0"0,7 2-1009 0 0,7-1-184 0 0,7 1 24 0 0,11 1-56 0 0,2 0 72 0 0,10 2 40 0 0,3 2-8 0 0,1 4-8 0 0,6 4-337 0 0,-9 1-2871 0 0,-1 7 2231 0 0,-11 4-2455 0 0,-6 0 15 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1231.85">3690 1809 10962 0 0,'-19'-8'1232'0'0,"11"5"-696"0"0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-7-6 0 0 0,13 9-521 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,2-2 1 0 0,31-26-305 0 0,-26 23 340 0 0,17-14-60 0 0,2 1 0 0 0,0 1-1 0 0,50-22 1 0 0,93-25-98 0 0,36-3-1647 0 0,102-41-7670 0 0,-226 77 5044 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1355.49">5072 659 13179 0 0,'-4'-7'464'0'0,"1"2"280"0"0,6 4-1016 0 0,10 4-264 0 0,11 1 104 0 0,18 5-120 0 0,10 2 104 0 0,74 12-11691 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1513.66">5413 1510 15763 0 0,'-10'-24'1689'0'0,"8"2"-985"0"0,10 0-24 0 0,21-5-336 0 0,16-5-288 0 0,19 0-128 0 0,9 1-24 0 0,7 4-32 0 0,3 4-56 0 0,13 4-1968 0 0,0-2-1905 0 0,-1 6-352 0 0,-7 1 4473 0 0,-6-7-4169 0 0,10-8 16 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:21:20.113"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3256 5504 9122 0 0,'-215'-11'4449'0'0,"-105"12"-3539"0"0,-82-2-601 0 0,-9-21-50 0 0,-5-28 77 0 0,307 29-183 0 0,-186-60 0 0 0,224 55-110 0 0,0-4-1 0 0,2-2 0 0 0,-92-59 1 0 0,113 57-42 0 0,2-2 1 0 0,1-2 0 0 0,2-1 0 0 0,1-3-1 0 0,3-1 1 0 0,1-2 0 0 0,3-2-1 0 0,-53-90 1 0 0,42 52-86 0 0,3-3 0 0 0,4-2 0 0 0,5-1-1 0 0,-35-140 1 0 0,50 150 2 0 0,4 0 0 0 0,3-1 0 0 0,4 0 0 0 0,3 0 0 0 0,4-1 0 0 0,3 1-1 0 0,4 0 1 0 0,4 0 0 0 0,4 0 0 0 0,2 1 0 0 0,55-154 0 0 0,-28 133 25 0 0,4 1 1 0 0,5 3 0 0 0,3 2-1 0 0,5 2 1 0 0,76-90 0 0 0,-25 55-137 0 0,4 4-1 0 0,213-177 1 0 0,-107 125-208 0 0,7 11 0 0 0,8 9 0 0 0,5 11-1 0 0,8 10 1 0 0,4 12 0 0 0,422-144 0 0 0,-182 111 295 0 0,682-125 1 0 0,-320 178 577 0 0,-599 94 21 0 0,347 30 0 0 0,-466-7-267 0 0,0 6 0 0 0,-2 7 1 0 0,-1 5-1 0 0,255 96 0 0 0,-305-91-152 0 0,-2 3 0 0 0,-1 4-1 0 0,-3 3 1 0 0,-1 4 0 0 0,-3 3 0 0 0,-2 3-1 0 0,-3 4 1 0 0,91 98 0 0 0,-96-80-41 0 0,-4 2 1 0 0,-3 3-1 0 0,-3 2 1 0 0,42 92 0 0 0,-25-21 46 0 0,80 248 0 0 0,-102-240-197 0 0,48 302 1 0 0,-81-338 12 0 0,-5 0 1 0 0,-6 1-1 0 0,-12 131 1 0 0,-2-185 145 0 0,-2 1 0 0 0,-4-2 1 0 0,-3 0-1 0 0,-3-1 0 0 0,-4-1 1 0 0,-3-1-1 0 0,-41 76 0 0 0,19-57 184 0 0,-3-3 1 0 0,-4-2-1 0 0,-4-2 0 0 0,-129 134 1 0 0,103-134-38 0 0,-3-5 1 0 0,-4-3 0 0 0,-3-5 0 0 0,-190 104 0 0 0,95-77-41 0 0,-366 128-1 0 0,345-159-253 0 0,-283 52-1 0 0,-228-18-1316 0 0,372-75-474 0 0,266-24 390 0 0,1-4 0 0 0,-95-14 0 0 0,72-7-2274 0 0,6-5-568 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="806.25">6186 5541 7666 0 0,'-22'15'546'0'0,"-2"-1"9"0"0,1 2 0 0 0,0 0 1 0 0,1 1-1 0 0,2 1 0 0 0,-1 2 0 0 0,2 0 0 0 0,-26 34 0 0 0,17-9-562 0 0,-41 86-1 0 0,-12 59 66 0 0,59-136-27 0 0,-66 185-223 0 0,73-191-663 0 0,3 0 1 0 0,2 1-1 0 0,-5 54 1 0 0,16-51-1699 0 0,-1-50 2324 0 0,0 0 1 0 0,0 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,3 2 0 0 0,9 1-1990 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="979.63">6235 5355 12443 0 0,'7'-3'46'0'0,"1"-1"0"0"0,-1 1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,14 2 0 0 0,9 3 122 0 0,-1 1-1 0 0,32 10 0 0 0,-18-4-3 0 0,188 40 264 0 0,-93-23-1141 0 0,137 47 0 0 0,-216-55-1482 0 0,-26-6-2743 0 0,61 41-633 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1171.56">6207 5596 16700 0 0,'-2'8'-2'0'0,"0"-1"1"0"0,0 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,2 9-1 0 0,-1-7 8 0 0,7 60 44 0 0,2 0 0 0 0,4-1 0 0 0,3-1 0 0 0,3 0 0 0 0,35 79 1 0 0,9-3-215 0 0,104 168 0 0 0,78 54-6694 0 0,-36-60-42 0 0,-170-237 4001 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2297.03">7828 6722 6553 0 0,'-13'-19'560'0'0,"5"8"-28"0"0,0 0-1 0 0,1-1 0 0 0,0-1 1 0 0,-8-19-1 0 0,14 29-468 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,3-3 0 0 0,15-13 12 0 0,1 0-1 0 0,1 2 1 0 0,0 0-1 0 0,1 2 1 0 0,33-17-1 0 0,129-54 214 0 0,-123 61-252 0 0,2 2-1 0 0,1 3 1 0 0,0 3 0 0 0,1 3-1 0 0,1 2 1 0 0,114-4 0 0 0,-103 14 23 0 0,1 4 0 0 0,141 20 0 0 0,-184-15-137 0 0,0 1-1 0 0,-1 2 1 0 0,0 1 0 0 0,-1 2 0 0 0,0 2 0 0 0,-1 0-1 0 0,0 3 1 0 0,38 26 0 0 0,-50-29-238 0 0,0 1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 2 1 0 0,26 32-1 0 0,-40-46 276 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-2 0 1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,-4 5 0 0 0,-4 4 65 0 0,0-1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,-29 20 0 0 0,-121 61 158 0 0,137-79-159 0 0,-7 2 26 0 0,0-1 0 0 0,-1-1 0 0 0,0-2 0 0 0,-1-2 0 0 0,0-1 0 0 0,-1-2-1 0 0,0-1 1 0 0,0-2 0 0 0,0-2 0 0 0,0-1 0 0 0,-1-2 0 0 0,1-1 0 0 0,0-3 0 0 0,-46-10-1 0 0,62 9 122 0 0,1-1-1 0 0,0-2 0 0 0,1 1 1 0 0,0-2-1 0 0,0-1 0 0 0,1 0 1 0 0,0-2-1 0 0,-16-14 0 0 0,3 4 409 0 0,27 20-429 0 0,-5-3 363 0 0,15 6-784 0 0,-2 2 276 0 0,-1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,2 7 1 0 0,1 7 188 0 0,-1 0 0 0 0,2 25 0 0 0,-5-39-187 0 0,4 59 314 0 0,-3 0-1 0 0,-3 0 1 0 0,-2 0-1 0 0,-4 0 1 0 0,-21 88-1 0 0,0-41-172 0 0,-5-2 1 0 0,-54 116-1 0 0,42-128 4 0 0,-62 93 0 0 0,55-101-162 0 0,46-75-41 0 0,-23 44-165 0 0,28-52 67 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 6 0 0 0,0-10 27 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,2-1-1 0 0,33-17-2801 0 0,-20 8 2126 0 0,0-1 1 0 0,-1-1-1 0 0,19-20 1 0 0,15-18-1974 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2454.9">10021 7078 12459 0 0,'9'-30'368'0'0,"6"3"88"0"0,10 5-544 0 0,12 1-40 0 0,9 0 48 0 0,8 2-32 0 0,7 1 136 0 0,-2 5-128 0 0,1 5-528 0 0,-10 8-25 0 0,-8 8-2503 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2592.3">9802 7729 10322 0 0,'13'-13'272'0'0,"10"-3"-208"0"0,7-7-40 0 0,14-4 0 0 0,4-4 80 0 0,17 0-48 0 0,10 4 16 0 0,6 2-24 0 0,12 3-24 0 0,-1 1-328 0 0,-3 0-752 0 0,3 2 56 0 0,1-1-2521 0 0,95-21-1600 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2909.13">11270 6914 7866 0 0,'-45'-75'3853'0'0,"53"75"-3033"0"0,7 7-814 0 0,353 235 1332 0 0,-165-102-1003 0 0,18-4-142 0 0,36 24-1448 0 0,-219-132-400 0 0,-1 2 1 0 0,-2 1-1 0 0,-1 2 0 0 0,59 73 0 0 0,-30-23-3219 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3114.11">12405 6877 13347 0 0,'-11'-1'98'0'0,"-1"1"0"0"0,1 1 1 0 0,-1-1-1 0 0,1 2 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 1 0 0,0 1-1 0 0,0-1 0 0 0,-9 11 0 0 0,-15 20-85 0 0,1 0-1 0 0,-53 85 1 0 0,-38 98 67 0 0,34-56 6 0 0,-50 57-20 0 0,-30 53-1776 0 0,164-266 1322 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-3 13 0 0 0,6-20 164 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,2 5 0 0 0,16 16-3002 0 0,-4-13 660 0 0,53 14 243 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:33.265"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1064 1 9978 0 0,'-80'77'320'0'0,"-13"17"1801"0"0,59-55-3266 0 0,-3 13-695 0 0,-6 0-344 0 0,-3-2-137 0 0,-2 2 2337 0 0,-2 0-2488 0 0,-2-5 7 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="159.81">33 856 12923 0 0,'6'-3'-340'0'0,"201"-82"1355"0"0,-43 14-706 0 0,206-65-814 0 0,-135 54-3758 0 0,-194 71-88 0 0,90-14-429 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="381.48">0 1357 16331 0 0,'1'1'3'0'0,"-1"0"-1"0"0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 5 0 0,26 16 14 0 0,1-2-1 0 0,0-1 1 0 0,1-2 0 0 0,0-1 0 0 0,1 0-1 0 0,0-3 1 0 0,1 0 0 0 0,39 2 0 0 0,13-3-602 0 0,154-11 0 0 0,-211 3 296 0 0,109-3-2959 0 0,-112 5 1736 0 0,0 2-1 0 0,0 0 0 0 0,39 9 1 0 0,-29 2-1290 0 0,-5 2-278 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="778.95">110 1463 7626 0 0,'0'-4'232'0'0,"-1"-1"1"0"0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,4-3-1 0 0,8-8-277 0 0,1 0 0 0 0,1 2 0 0 0,23-15-1 0 0,-11 7 743 0 0,31-20-222 0 0,2 1 0 0 0,2 4 0 0 0,117-49 1 0 0,-67 42-294 0 0,177-41 1 0 0,-96 47-172 0 0,-170 34-262 0 0,0 1-1 0 0,0 1 1 0 0,0 2-1 0 0,0 0 1 0 0,47 10-1 0 0,-66-10 134 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,8 5 0 0 0,-12-7 85 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,-1 1-1 0 0,0 1 1 0 0,-13 15-180 0 0,0-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1-1-1 0 0,-1 0 0 0 0,-1-2 1 0 0,0 0-1 0 0,-1-1 1 0 0,-32 15-1 0 0,-19 4 110 0 0,-109 32 1 0 0,154-55 79 0 0,-32 11 44 0 0,0-3 1 0 0,-92 14 0 0 0,134-28-6 0 0,0-1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0-2 0 0 0,0 0-1 0 0,0 0 1 0 0,0-2-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,0-1 0 0 0,1-1-1 0 0,-24-14 1 0 0,32 17-23 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,5-15 0 0 0,-1 7 141 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 1 0 0,2 0-1 0 0,-1 1 0 0 0,2-1 0 0 0,0 2 0 0 0,0-1 0 0 0,1 2 1 0 0,25-22-1 0 0,-30 28-30 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 2 1 0 0,14-4-1 0 0,-18 5-67 0 0,0 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,4 7 0 0 0,3 4 135 0 0,-1 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,2 24 1 0 0,0 17 75 0 0,-2 90-1 0 0,-4-111-251 0 0,-8 266-632 0 0,5-209-2494 0 0,0 8-3634 0 0,0-11 1872 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="954.39">417 2025 5281 0 0,'-21'-17'5271'0'0,"21"15"-4942"0"0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1-2 0 0 0,1 1-297 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,3-2-1 0 0,8-12-10 0 0,143-162 418 0 0,-130 153-1367 0 0,1 1 1 0 0,1 1-1 0 0,1 1 1 0 0,45-26-1 0 0,-68 46 148 0 0,-1 0-1 0 0,1 0 1 0 0,1 0-1 0 0,10-2 0 0 0,-15 4 622 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,1 2 0 0 0,8 9-1717 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1113.65">548 2308 392 0 0,'-24'28'1009'0'0,"15"-18"102"0"0,1 0 1 0 0,0 0-1 0 0,-11 19 1 0 0,44-35 1476 0 0,7-12-1934 0 0,-1-1 0 0 0,-1-1-1 0 0,46-42 1 0 0,-1 2-239 0 0,191-134 383 0 0,-80 74-4270 0 0,-33 28-1597 0 0,-85 49 1355 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1415.58">1494 1188 14715 0 0,'14'-19'25'0'0,"2"0"-1"0"0,0 1 0 0 0,1 1 1 0 0,0 0-1 0 0,1 1 1 0 0,1 1-1 0 0,1 1 0 0 0,38-20 1 0 0,-6 7 12 0 0,1 3 0 0 0,80-25 0 0 0,-113 42-85 0 0,0 1 0 0 0,1 1 1 0 0,0 2-1 0 0,0-1 0 0 0,0 2 0 0 0,0 1 1 0 0,42 3-1 0 0,-54-1-7 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 1 0 0 0,8 13 0 0 0,-5-4-38 0 0,-1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-4 25 1 0 0,-4 4-128 0 0,-1 0 0 0 0,-3-1 0 0 0,-37 90 0 0 0,36-102 329 0 0,-3 0 1 0 0,-1-1-1 0 0,-1-1 1 0 0,-2-1-1 0 0,-1-1 1 0 0,-47 52-1 0 0,57-72-206 0 0,0 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0-1 0 0 0,-18 7 1 0 0,21-11-329 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1-1 0 0 0,-1 0-1 0 0,-14-4 1 0 0,16 2-130 0 0,-1 0 0 0 0,1-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0-1-1 0 0,-14-12 0 0 0,22 18 546 0 0,-1 0-94 0 0,-8-15-406 0 0,-22-55-92 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1543.21">1678 1108 1480 0 0,'11'-33'264'0'0,"27"-71"2886"0"0,-32 90-2103 0 0,1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 1 0 0,16-10 2403 0 0,-24 23-3409 0 0,2 13 754 0 0,0 14-381 0 0,-2-27-383 0 0,-1 86 721 0 0,-3 0-1 0 0,-18 91 0 0 0,-46 167-630 0 0,54-279-188 0 0,-73 390-3448 0 0,68-314-33 0 0,6-27-3642 0 0,3-23 4267 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1924.46">3213 406 14563 0 0,'-21'3'-32'0'0,"-1"1"0"0"0,1 1-1 0 0,-1 1 1 0 0,2 1 0 0 0,-1 1 0 0 0,1 1 0 0 0,0 1-1 0 0,1 0 1 0 0,0 2 0 0 0,0 0 0 0 0,2 1 0 0 0,-27 24-1 0 0,-66 43-550 0 0,58-45 357 0 0,51-35 191 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 2 0 0 0,5 10 178 0 0,10 22-74 0 0,-1 2 0 0 0,-2 0-1 0 0,-2 0 1 0 0,-1 1 0 0 0,-2 1 0 0 0,7 57 0 0 0,3 239 2087 0 0,-14-166-1180 0 0,-4-132-970 0 0,13 136 392 0 0,-11-149-714 0 0,1 0 1 0 0,2-1 0 0 0,0 0-1 0 0,1 0 1 0 0,14 28 0 0 0,-5-23-3382 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2177.77">2873 1069 13235 0 0,'-1'-1'56'0'0,"1"1"-1"0"0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,2 0 0 0 0,32-22-695 0 0,-24 16 869 0 0,29-21-198 0 0,1 2 0 0 0,85-41 1 0 0,-102 57-55 0 0,1 0 1 0 0,-1 2 0 0 0,1 2 0 0 0,1 0-1 0 0,-1 1 1 0 0,1 1 0 0 0,37-1 0 0 0,-55 5 8 0 0,-1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,8 7 1 0 0,-8-4 17 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,3 13 1 0 0,2 12 21 0 0,-2 0 0 0 0,-1 1 0 0 0,-2 0 0 0 0,-1 56 0 0 0,-9 163-2086 0 0,3-216 145 0 0,-2-1 0 0 0,-2 0 0 0 0,-1-1 0 0 0,-23 65 0 0 0,15-66-1143 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2321.56">3032 1466 12707 0 0,'-9'-13'2656'0'0,"9"4"-2984"0"0,12-3-232 0 0,7-5 112 0 0,10-3-72 0 0,6-4 432 0 0,4 0-656 0 0,1-1-88 0 0,0 4-241 0 0,-4 3-495 0 0,26 0-7626 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2463.42">3199 1738 11610 0 0,'-26'3'1529'0'0,"7"0"-1585"0"0,4 0-240 0 0,8-3-256 0 0,10-12-1993 0 0,4-1 865 0 0,29-33-6322 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2797.62">3996 844 15027 0 0,'-14'8'273'0'0,"1"0"0"0"0,0 1-1 0 0,0 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,-11 15-1 0 0,-7 12-692 0 0,-25 42 0 0 0,32-45 344 0 0,23-34-15 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 1 1 0 0,0-1 46 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,3-1 0 0 0,58-18 415 0 0,-61 18-407 0 0,172-78 500 0 0,27-9-122 0 0,-176 79-252 0 0,1 2 0 0 0,0 1 0 0 0,0 1 0 0 0,0 1 0 0 0,1 2 0 0 0,42 0 0 0 0,-50 2-43 0 0,1 2 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 1 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1-1 0 0,26 15 1 0 0,-35-16-34 0 0,0 1 0 0 0,0-1 0 0 0,0 2-1 0 0,0-1 1 0 0,-1 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-2 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,2 15-1 0 0,-2 1 55 0 0,-1 0 0 0 0,-1 0 0 0 0,-2 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-1-1-1 0 0,-13 36 1 0 0,2-15-9 0 0,-2-2-1 0 0,-2 0 1 0 0,-1-1 0 0 0,-37 54-1 0 0,41-74-345 0 0,-1 0 0 0 0,-1 0 0 0 0,-1-2 0 0 0,-36 31 0 0 0,40-40-815 0 0,-1 0 0 0 0,-32 17 0 0 0,36-23-291 0 0,0-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-22 5 0 0 0,-3-5-3259 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2924.74">4125 1417 11010 0 0,'-25'-3'5559'0'0,"29"5"-5590"0"0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,8 0-1 0 0,19 3 109 0 0,2 7-7 0 0,-1 1 0 0 0,40 20 0 0 0,4 2 13 0 0,132 35-692 0 0,-102-40-5890 0 0,-73-19 2962 0 0,71 20-2452 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:44.742"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">56 19 4833 0 0,'-9'-2'2233'0'0,"-37"-3"-1245"0"0,76 16 947 0 0,24-3-1400 0 0,0-2 1 0 0,0-3-1 0 0,94-6 1 0 0,-74 0-440 0 0,357-12 53 0 0,416-4 135 0 0,-450 24-77 0 0,-22-1-2038 0 0,-111-3-6338 0 0,-188-1 5310 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:45.863"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 151 9194 0 0,'50'-45'4356'0'0,"2"7"-3388"0"0,-38 30-1033 0 0,-1 1 1 0 0,1 0 0 0 0,0 1-1 0 0,0 1 1 0 0,1 0-1 0 0,23-4 1 0 0,48-2-49 0 0,-1 4 0 0 0,122 5 0 0 0,-87 3 100 0 0,5-2 2 0 0,366 1-609 0 0,-2 35-1632 0 0,43 26-785 0 0,-149-32-3787 0 0,-263-22 5861 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink8.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:46.718"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 45 12459 0 0,'0'-2'87'0'0,"0"0"19"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,2-4 0 0 0,-1 6-133 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,3 1-1 0 0,334-6-69 0 0,-15-1 492 0 0,429 33-331 0 0,-336-10-1717 0 0,1-6-3712 0 0,-130-4 1837 0 0,-138-5 373 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink9.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T12:22:50.792"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.2" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 222 7690 0 0,'8'-6'505'0'0,"0"0"0"0"0,1 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,17-4 0 0 0,75-10-1258 0 0,-66 14 1123 0 0,1427-124 24 0 0,-1347 124-671 0 0,1026-22-4509 0 0,-1081 27 1640 0 0,146 3-377 0 0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1011,12 +2655,12 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="3:15">
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="D10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
       <c r="H10" t="s">
         <v>2</v>
       </c>
@@ -1049,10 +2693,10 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="3:15">
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="14"/>
+      <c r="D16" s="16"/>
       <c r="I16" s="2"/>
       <c r="O16" s="2"/>
     </row>
@@ -1060,7 +2704,7 @@
       <c r="C17" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="15"/>
+      <c r="D17" s="18"/>
       <c r="I17" s="2"/>
       <c r="O17" s="2"/>
     </row>
@@ -1075,50 +2719,50 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="3:15">
-      <c r="C19" s="18"/>
-      <c r="D19" s="16"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
       <c r="I19" s="2"/>
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="3:15">
-      <c r="C20" s="18"/>
-      <c r="D20" s="16"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="13"/>
       <c r="I20" s="2"/>
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="3:15">
-      <c r="C21" s="18"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
       <c r="I21" s="2"/>
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="3:15">
-      <c r="C22" s="18"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="13"/>
       <c r="I22" s="2"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="3:15">
-      <c r="C23" s="18"/>
-      <c r="D23" s="16"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="13"/>
       <c r="I23" s="2"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="3:15">
-      <c r="C24" s="18"/>
-      <c r="D24" s="16"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="13"/>
       <c r="I24" s="2"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="3:15">
-      <c r="C25" s="18"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="13"/>
       <c r="I25" s="2"/>
       <c r="O25" s="2"/>
     </row>
     <row r="26" spans="3:15">
       <c r="C26" s="3"/>
-      <c r="D26" s="16"/>
+      <c r="D26" s="13"/>
       <c r="I26" s="2"/>
       <c r="O26" s="2"/>
     </row>
@@ -1244,4 +2888,110 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C250D7-AE9F-428A-9C91-CFE1A0C9E14D}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A58E9B-0E21-46D4-B35A-F135C635A677}">
+  <dimension ref="A2:X35"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="6:9">
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="6:9">
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="6:9">
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="9:9">
+      <c r="I33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="9:9">
+      <c r="I34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="9:9">
+      <c r="I35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>